--- a/app/pipeline_output/INDIFI/mapping_INDIFI_COMBINED.xlsx
+++ b/app/pipeline_output/INDIFI/mapping_INDIFI_COMBINED.xlsx
@@ -12,7 +12,7 @@
     <sheet name="For Review" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Mapping'!$A$1:$I$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Mapping'!$A$1:$I$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'For Review'!$A$1:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -564,40 +564,40 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BRANCH</t>
+          <t>LOAN ID</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTPARTNERBRANCHNAME</t>
+          <t>LOANID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.partnerBranchName</t>
+          <t>loanAccount.oldAccountNO</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BRANCH' → 'APPLICANTPARTNERBRANCHNAME' (frequency=14)</t>
+          <t>Exact match: normalized 'LOAN ID' matches 'LOANID'</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -609,12 +609,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BRANCH CLASSIFICATION</t>
+          <t>BRANCH</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -624,12 +624,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER10</t>
+          <t>APPLICANTPARTNERBRANCHNAME</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.10.value</t>
+          <t>loanAccount.loanAccountAdditional.partnerBranchName</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
@@ -642,7 +642,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BRANCH CLASSIFICATION' → 'LOANPARAMETER10' (frequency=13)</t>
+          <t>Alias match (tier2): 'BRANCH' → 'APPLICANTPARTNERBRANCHNAME' (frequency=14)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CUSTOMER_CENTER</t>
+          <t>BRANCH CLASSIFICATION</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER50</t>
+          <t>LOANPARAMETER1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.50.value</t>
+          <t>loanAccount.loanParameters.1.value</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CUSTOMER_CENTER' → 'LOANPARAMETER50' (frequency=16)</t>
+          <t>Alias match (tier2): 'BRANCH CLASSIFICATION' → 'LOANPARAMETER10' (frequency=13)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -699,12 +699,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BRANCH CITY</t>
+          <t>CUSTOMER_CENTER</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER11</t>
+          <t>LOANPARAMETER2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.11.value</t>
+          <t>loanAccount.loanParameters.2.value</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BRANCH CITY' → 'LOANPARAMETER11' (frequency=14)</t>
+          <t>Alias match (tier2): 'CUSTOMER_CENTER' → 'LOANPARAMETER50' (frequency=16)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -744,12 +744,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BRANCH STATE</t>
+          <t>BRANCH CITY</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER51</t>
+          <t>LOANPARAMETER3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.51.value</t>
+          <t>loanAccount.loanParameters.3.value</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
@@ -777,7 +777,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BRANCH STATE' → 'LOANPARAMETER51' (frequency=14)</t>
+          <t>Alias match (tier2): 'BRANCH CITY' → 'LOANPARAMETER11' (frequency=14)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GROUP NAME</t>
+          <t>BRANCH STATE</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -804,25 +804,25 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>GROUPNAME</t>
+          <t>LOANPARAMETER4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.groupName</t>
+          <t>loanAccount.loanParameters.4.value</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'GROUP NAME' matches 'GROUPNAME'</t>
+          <t>Alias match (tier2): 'BRANCH STATE' → 'LOANPARAMETER51' (frequency=14)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -834,12 +834,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FIELD EXECUTIVE NAME</t>
+          <t>GROUP NAME</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -849,25 +849,25 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER6</t>
+          <t>GROUPNAME</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.6.value</t>
+          <t>loanAccount.groupName</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'FIELD EXECUTIVE NAME' → 'LOANPARAMETER6' (frequency=20)</t>
+          <t>Exact match: normalized 'GROUP NAME' matches 'GROUPNAME'</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DEALER NAME</t>
+          <t>FIELD EXECUTIVE NAME</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER122</t>
+          <t>LOANPARAMETER5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.122.value</t>
+          <t>loanAccount.loanParameters.5.value</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DEALER NAME' → 'LOANPARAMETER122' (frequency=12)</t>
+          <t>Alias match (tier2): 'FIELD EXECUTIVE NAME' → 'LOANPARAMETER6' (frequency=20)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SUB DEALER NAME</t>
+          <t>DEALER NAME</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -939,25 +939,25 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER123</t>
+          <t>LOANPARAMETER6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.123.value</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.6.value</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'SUB DEALER NAME' → 'LOANPARAMETER123' (frequency=7)</t>
+          <t>Alias match (tier2): 'DEALER NAME' → 'LOANPARAMETER122' (frequency=12)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SPOUSE NAME</t>
+          <t>SUB DEALER NAME</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Partner Details</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -984,25 +984,25 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTSPOUSENAME</t>
+          <t>LOANPARAMETER7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.spouseFirstName</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.98</v>
+          <t>loanAccount.loanParameters.7.value</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'SPOUSE NAME' → 'APPLICANTSPOUSENAME' (frequency=43)</t>
+          <t>Alias match (tier3): 'SUB DEALER NAME' → 'LOANPARAMETER123' (frequency=7)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>FATHER'S NAME</t>
+          <t>SPOUSE NAME</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1029,25 +1029,25 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER175</t>
+          <t>APPLICANTSPOUSENAME</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.175.value</t>
+          <t>loanAccount.customer.spouseFirstName</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'FATHER'S NAME' → 'LOANPARAMETER175' (frequency=10)</t>
+          <t>Alias match (tier1): 'SPOUSE NAME' → 'APPLICANTSPOUSENAME' (frequency=43)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1059,12 +1059,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MOTHER'S NAME</t>
+          <t>FATHER'S NAME</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1074,25 +1074,25 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER177</t>
+          <t>LOANPARAMETER8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.177.value</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.8.value</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'MOTHER'S NAME' → 'LOANPARAMETER177' (frequency=7)</t>
+          <t>Alias match (tier2): 'FATHER'S NAME' → 'LOANPARAMETER175' (frequency=10)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SURNAME</t>
+          <t>MOTHER'S NAME</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER75</t>
+          <t>LOANPARAMETER9</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.75.value</t>
+          <t>loanAccount.loanParameters.9.value</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'SURNAME' → 'LOANPARAMETER75' (frequency=7)</t>
+          <t>Alias match (tier3): 'MOTHER'S NAME' → 'LOANPARAMETER177' (frequency=7)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1149,12 +1149,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CITY</t>
+          <t>SURNAME</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1164,25 +1164,25 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERDISTRICT</t>
+          <t>LOANPARAMETER10</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.district</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.98</v>
+          <t>loanAccount.loanParameters.10.value</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'CITY' → 'APPLICANTCUSTOMERDISTRICT' (frequency=46)</t>
+          <t>Alias match (tier3): 'SURNAME' → 'LOANPARAMETER75' (frequency=7)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>CITY</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1209,25 +1209,25 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>APPLICANTCUSTOMERDISTRICT</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>customer.state</t>
+          <t>loanAccount.customer.district</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'STATE' matches 'STATE'</t>
+          <t>Alias match (tier1): 'CITY' → 'APPLICANTCUSTOMERDISTRICT' (frequency=46)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CAST</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1254,25 +1254,25 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER167</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.167.value</t>
+          <t>customer.state</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CAST' → 'LOANPARAMETER167' (frequency=10)</t>
+          <t>Exact match: normalized 'STATE' matches 'STATE'</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1284,12 +1284,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GENDER</t>
+          <t>CAST</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>GENDER</t>
+          <t>LOANPARAMETER11</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>customer.gender</t>
+          <t>loanAccount.loanParameters.11.value</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'GENDER' matches 'GENDER'</t>
+          <t>Alias match (tier2): 'CAST' → 'LOANPARAMETER167' (frequency=10)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MARITAL STATUS</t>
+          <t>GENDER</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MARITALSTATUS</t>
+          <t>GENDER</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>customer.maritalStatus</t>
+          <t>customer.gender</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'MARITAL STATUS' matches 'MARITALSTATUS'</t>
+          <t>Exact match: normalized 'GENDER' matches 'GENDER'</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CONSTITUTION</t>
+          <t>MARITAL STATUS</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1389,25 +1389,25 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ENTERPRISEBUSINESSCONSTITUTION</t>
+          <t>MARITALSTATUS</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.enterprise.businessConstitution</t>
+          <t>customer.maritalStatus</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CONSTITUTION' → 'ENTERPRISEBUSINESSCONSTITUTION' (frequency=18)</t>
+          <t>Exact match: normalized 'MARITAL STATUS' matches 'MARITALSTATUS'</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CITIZENSHIP</t>
+          <t>CONSTITUTION</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCOUNTRY</t>
+          <t>ENTERPRISEBUSINESSCONSTITUTION</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.country</t>
+          <t>loanAccount.customer.enterprise.businessConstitution</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CITIZENSHIP' → 'APPLICANTCOUNTRY' (frequency=21)</t>
+          <t>Alias match (tier2): 'CONSTITUTION' → 'ENTERPRISEBUSINESSCONSTITUTION' (frequency=18)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CONTACT NO.</t>
+          <t>CITIZENSHIP</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER77</t>
+          <t>APPLICANTCOUNTRY</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.77.value</t>
+          <t>loanAccount.customer.country</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CONTACT NO.' → 'LOANPARAMETER77' (frequency=10)</t>
+          <t>Alias match (tier2): 'CITIZENSHIP' → 'APPLICANTCOUNTRY' (frequency=21)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1509,12 +1509,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>OFFICE NAME</t>
+          <t>CONTACT NO.</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1524,25 +1524,25 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER78</t>
+          <t>LOANPARAMETER12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.78.value</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.12.value</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'OFFICE NAME' → 'LOANPARAMETER78' (frequency=7)</t>
+          <t>Alias match (tier2): 'CONTACT NO.' → 'LOANPARAMETER77' (frequency=10)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>DESIGNATION</t>
+          <t>OFFICE NAME</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1569,25 +1569,25 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTDESIGNATION</t>
+          <t>LOANPARAMETER13</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.designation</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>0.92</v>
+          <t>loanAccount.loanParameters.13.value</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DESIGNATION' → 'APPLICANTDESIGNATION' (frequency=11)</t>
+          <t>Alias match (tier3): 'OFFICE NAME' → 'LOANPARAMETER78' (frequency=7)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OFFICE CITY</t>
+          <t>DESIGNATION</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER60</t>
+          <t>APPLICANTDESIGNATION</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.60.value</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.designation</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'OFFICE CITY' → 'LOANPARAMETER60' (frequency=6)</t>
+          <t>Alias match (tier2): 'DESIGNATION' → 'APPLICANTDESIGNATION' (frequency=11)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1644,12 +1644,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>OFFICE STATE</t>
+          <t>OFFICE CITY</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER61</t>
+          <t>LOANPARAMETER14</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.61.value</t>
+          <t>loanAccount.loanParameters.14.value</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'OFFICE STATE' → 'LOANPARAMETER61' (frequency=6)</t>
+          <t>Alias match (tier3): 'OFFICE CITY' → 'LOANPARAMETER60' (frequency=6)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>OCCUPATION STATUS</t>
+          <t>OFFICE STATE</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1704,25 +1704,25 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTOCCUPATION</t>
+          <t>LOANPARAMETER15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.occupation1</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>0.92</v>
+          <t>loanAccount.loanParameters.15.value</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'OCCUPATION STATUS' → 'APPLICANTOCCUPATION' (frequency=10)</t>
+          <t>Alias match (tier3): 'OFFICE STATE' → 'LOANPARAMETER61' (frequency=6)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1734,40 +1734,40 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PURPOSE OF LOAN</t>
+          <t>OCCUPATION STATUS</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Details</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>LOANPURPOSE2</t>
+          <t>APPLICANTOCCUPATION</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanPurpose2</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.occupation1</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'PURPOSE OF LOAN' → 'LOANPURPOSE2' (frequency=7)</t>
+          <t>Alias match (tier2): 'OCCUPATION STATUS' → 'APPLICANTOCCUPATION' (frequency=10)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1779,40 +1779,40 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NATURE OF BUSINESS</t>
+          <t>PURPOSE OF LOAN</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Details</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER6</t>
+          <t>LOANPURPOSE2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.6.value</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>0.92</v>
+          <t>loanAccount.loanPurpose2</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'NATURE OF BUSINESS' → 'LOANPARAMETER6' (frequency=24)</t>
+          <t>Alias match (tier3): 'PURPOSE OF LOAN' → 'LOANPURPOSE2' (frequency=7)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PHYSICAL_DISABILITY</t>
+          <t>NATURE OF BUSINESS</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Details</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER54</t>
+          <t>LOANPARAMETER16</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.54.value</t>
+          <t>loanAccount.loanParameters.16.value</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'PHYSICAL_DISABILITY' → 'LOANPARAMETER54' (frequency=11)</t>
+          <t>Alias match (tier2): 'NATURE OF BUSINESS' → 'LOANPARAMETER6' (frequency=24)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>WEAKER</t>
+          <t>PHYSICAL_DISABILITY</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Details</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER56</t>
+          <t>LOANPARAMETER17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.56.value</t>
+          <t>loanAccount.loanParameters.17.value</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'WEAKER' → 'LOANPARAMETER56' (frequency=11)</t>
+          <t>Alias match (tier2): 'PHYSICAL_DISABILITY' → 'LOANPARAMETER54' (frequency=11)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>NET INCOME (MONTHLY)</t>
+          <t>WEAKER</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Details</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1929,25 +1929,25 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>BORROWERINCOME</t>
+          <t>LOANPARAMETER18</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.netIncomeOfBorrower</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.18.value</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'NET INCOME (MONTHLY)' → 'BORROWERINCOME' (frequency=7)</t>
+          <t>Alias match (tier2): 'WEAKER' → 'LOANPARAMETER56' (frequency=11)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GROSS INCOME (Monthly)</t>
+          <t>NET INCOME (MONTHLY)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Details</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1974,25 +1974,25 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER106</t>
+          <t>BORROWERINCOME</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.106.value</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0.92</v>
+          <t>loanAccount.loanAccountAdditional.netIncomeOfBorrower</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'GROSS INCOME (Monthly)' → 'LOANPARAMETER106' (frequency=10)</t>
+          <t>Alias match (tier3): 'NET INCOME (MONTHLY)' → 'BORROWERINCOME' (frequency=7)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2004,12 +2004,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NO OF EMP</t>
+          <t>GROSS INCOME (Monthly)</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Details</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2019,25 +2019,25 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>NOOFEMPLOYEES</t>
+          <t>LOANPARAMETER19</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.enterprise.noOfRegularEmployees</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.19.value</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'NO OF EMP' → 'NOOFEMPLOYEES' (frequency=7)</t>
+          <t>Alias match (tier2): 'GROSS INCOME (Monthly)' → 'LOANPARAMETER106' (frequency=10)</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>PAN_NO</t>
+          <t>NO OF EMP</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Details</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERPANNO</t>
+          <t>NOOFEMPLOYEES</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.panNo</t>
+          <t>loanAccount.customer.enterprise.noOfRegularEmployees</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'PAN_NO' → 'APPLICANTCUSTOMERPANNO' (frequency=4)</t>
+          <t>Alias match (tier3): 'NO OF EMP' → 'NOOFEMPLOYEES' (frequency=7)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>VOTER_ID</t>
+          <t>PAN_NO</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Applicant)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2109,25 +2109,25 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>VOTERID</t>
+          <t>APPLICANTCUSTOMERPANNO</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerAdditional.voterId</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>1</v>
+          <t>loanAccount.customer.panNo</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'VOTER_ID' matches 'VOTERID'</t>
+          <t>Alias match (tier3): 'PAN_NO' → 'APPLICANTCUSTOMERPANNO' (frequency=4)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PASSPORT_NO</t>
+          <t>VOTER_ID</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Applicant)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>PASSPORTNO</t>
+          <t>VOTERID</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerAdditional.passportNo</t>
+          <t>loanAccount.customer.customerAdditional.voterId</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'PASSPORT_NO' matches 'PASSPORTNO'</t>
+          <t>Exact match: normalized 'VOTER_ID' matches 'VOTERID'</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AADHARCARD</t>
+          <t>PASSPORT_NO</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Applicant)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2199,25 +2199,25 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTAADHAARNO</t>
+          <t>PASSPORTNO</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.aadhaarNo</t>
+          <t>loanAccount.customer.customerAdditional.passportNo</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'AADHARCARD' → 'APPLICANTAADHAARNO' (frequency=12)</t>
+          <t>Exact match: normalized 'PASSPORT_NO' matches 'PASSPORTNO'</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GST NUMBER</t>
+          <t>AADHARCARD</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Applicant)</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2244,25 +2244,25 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>GSTNUMBER</t>
+          <t>APPLICANTAADHAARNO</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>customer.enterpriseRegistrations.0.registrationNumber</t>
+          <t>loanAccount.customer.aadhaarNo</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'GST NUMBER' matches 'GSTNUMBER'</t>
+          <t>Alias match (tier2): 'AADHARCARD' → 'APPLICANTAADHAARNO' (frequency=12)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2274,12 +2274,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LOGIN DATE</t>
+          <t>GST NUMBER</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Applicant)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2289,25 +2289,25 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>LOANAPPLICATIONDATE</t>
+          <t>GSTNUMBER</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanApplicationDate</t>
+          <t>customer.enterpriseRegistrations.0.registrationNumber</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'LOGIN DATE' → 'LOANAPPLICATIONDATE' (frequency=10)</t>
+          <t>Exact match: normalized 'GST NUMBER' matches 'GSTNUMBER'</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2319,12 +2319,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>DISB. DATE</t>
+          <t>LOGIN DATE</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>DISBDATE</t>
+          <t>LOANAPPLICATIONDATE</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.lenderApprovalDate</t>
+          <t>loanAccount.loanApplicationDate</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'DISB. DATE' matches 'DISBDATE'</t>
+          <t>Alias match (tier2): 'LOGIN DATE' → 'LOANAPPLICATIONDATE' (frequency=10)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>DOWN PAYMENT</t>
+          <t>DISB. DATE</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2379,25 +2379,25 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER132</t>
+          <t>DISBDATE</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.132.value</t>
+          <t>loanAccount.loanAccountAdditional.lenderApprovalDate</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DOWN PAYMENT' → 'LOANPARAMETER132' (frequency=10)</t>
+          <t>Exact match: normalized 'DISB. DATE' matches 'DISBDATE'</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>NO. OF INST.</t>
+          <t>DOWN PAYMENT</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>NUMBEROFINSTALMENTS</t>
+          <t>LOANPARAMETER20</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.tenure</t>
+          <t>loanAccount.loanParameters.20.value</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'NO. OF INST.' → 'NUMBEROFINSTALMENTS' (frequency=10)</t>
+          <t>Alias match (tier2): 'DOWN PAYMENT' → 'LOANPARAMETER132' (frequency=10)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>COLLECTION FREQUENCY</t>
+          <t>NO. OF INST.</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>REPAYMENTFREQUENCY</t>
+          <t>NUMBEROFINSTALMENTS</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.frequency</t>
+          <t>loanAccount.tenure</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'COLLECTION FREQUENCY' → 'REPAYMENTFREQUENCY' (frequency=10)</t>
+          <t>Alias match (tier2): 'NO. OF INST.' → 'NUMBEROFINSTALMENTS' (frequency=10)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MAS ROI</t>
+          <t>COLLECTION FREQUENCY</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2514,25 +2514,25 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>LENDER1INTERESTRATE</t>
+          <t>REPAYMENTFREQUENCY</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.colendingBankInterestRate</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.frequency</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'MAS ROI' → 'LENDER1INTERESTRATE' (frequency=9)</t>
+          <t>Alias match (tier2): 'COLLECTION FREQUENCY' → 'REPAYMENTFREQUENCY' (frequency=10)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2544,40 +2544,40 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MAS PROCESSING FEES</t>
+          <t>MAS ROI</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER8</t>
+          <t>LENDER1INTERESTRATE</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.8.value</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0.92</v>
+          <t>loanAccount.loanAccountAdditional.colendingBankInterestRate</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'MAS PROCESSING FEES' → 'LOANPARAMETER8' (frequency=10)</t>
+          <t>Alias match (tier3): 'MAS ROI' → 'LENDER1INTERESTRATE' (frequency=9)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2589,27 +2589,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MAS GST AMOUNT</t>
+          <t>MAS PROCESSING FEES</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER12</t>
+          <t>LOANPARAMETER21</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.12.value</t>
+          <t>loanAccount.loanParameters.21.value</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'MAS GST AMOUNT' → 'LOANPARAMETER12' (frequency=10)</t>
+          <t>Alias match (tier2): 'MAS PROCESSING FEES' → 'LOANPARAMETER8' (frequency=10)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2634,40 +2634,40 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>PARTNAR PROCESSING FEES</t>
+          <t>MAS GST AMOUNT</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>FEE6</t>
+          <t>LOANPARAMETER22</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee6</t>
+          <t>loanAccount.loanParameters.22.value</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Fee detection: field contains fee/charge keywords (fee, fees, processing)</t>
+          <t>Alias match (tier2): 'MAS GST AMOUNT' → 'LOANPARAMETER12' (frequency=10)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>PARTNAR OTHER'S CHARGES</t>
+          <t>PARTNAR PROCESSING FEES</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>FEE7</t>
+          <t>FEE6</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee7</t>
+          <t>loanAccount.fee6</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Fee detection: field contains fee/charge keywords (charges, charge)</t>
+          <t>Fee detection: field contains fee/charge keywords (fee, fees, processing)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2724,40 +2724,40 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>STAMP_DUTY</t>
+          <t>PARTNAR OTHER'S CHARGES</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>FEE5</t>
+          <t>FEE7</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee5</t>
+          <t>loanAccount.fee7</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'STAMP_DUTY' → 'FEE5' (frequency=15)</t>
+          <t>Fee detection: field contains fee/charge keywords (charge, charges)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2769,12 +2769,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>EMI AMOUNT</t>
+          <t>STAMP_DUTY</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTPROPOSEDEMI</t>
+          <t>FEE5</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.estimatedEmi</t>
+          <t>loanAccount.fee5</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'EMI AMOUNT' → 'APPLICANTPROPOSEDEMI' (frequency=10)</t>
+          <t>Alias match (tier2): 'STAMP_DUTY' → 'FEE5' (frequency=15)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2814,40 +2814,40 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1ST EMI DATE</t>
+          <t>EMI AMOUNT</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>FEE8</t>
+          <t>APPLICANTPROPOSEDEMI</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee8</t>
+          <t>loanAccount.estimatedEmi</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Fee detection: field contains fee/charge keywords (emi)</t>
+          <t>Alias match (tier2): 'EMI AMOUNT' → 'APPLICANTPROPOSEDEMI' (frequency=10)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2859,40 +2859,40 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LAST EMI DATE</t>
+          <t>1ST EMI DATE</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>LASTEMIDATE</t>
+          <t>FEE8</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.estimatedDateOfCompletion</t>
+          <t>loanAccount.fee8</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'LAST EMI DATE' matches 'LASTEMIDATE'</t>
+          <t>Fee detection: field contains fee/charge keywords (emi)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>CUSTOMER_PAYMENT</t>
+          <t>LAST EMI DATE</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2919,25 +2919,25 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER43</t>
+          <t>LASTEMIDATE</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.43.value</t>
+          <t>loanAccount.estimatedDateOfCompletion</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CUSTOMER_PAYMENT' → 'LOANPARAMETER43' (frequency=13)</t>
+          <t>Exact match: normalized 'LAST EMI DATE' matches 'LASTEMIDATE'</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2949,27 +2949,27 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>CHARGES DEDUCTION</t>
+          <t>CUSTOMER_PAYMENT</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER141</t>
+          <t>LOANPARAMETER23</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.141.value</t>
+          <t>loanAccount.loanParameters.23.value</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CHARGES DEDUCTION' → 'LOANPARAMETER141' (frequency=10)</t>
+          <t>Alias match (tier2): 'CUSTOMER_PAYMENT' → 'LOANPARAMETER43' (frequency=13)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2994,27 +2994,27 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>DISB MODE BY</t>
+          <t>CHARGES DEDUCTION</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER142</t>
+          <t>LOANPARAMETER24</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.142.value</t>
+          <t>loanAccount.loanParameters.24.value</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DISB MODE BY' → 'LOANPARAMETER142' (frequency=10)</t>
+          <t>Alias match (tier2): 'CHARGES DEDUCTION' → 'LOANPARAMETER141' (frequency=10)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>COLLECTION MODE</t>
+          <t>DISB MODE BY</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER143</t>
+          <t>LOANPARAMETER25</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.143.value</t>
+          <t>loanAccount.loanParameters.25.value</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'COLLECTION MODE' → 'LOANPARAMETER143' (frequency=16)</t>
+          <t>Alias match (tier2): 'DISB MODE BY' → 'LOANPARAMETER142' (frequency=10)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CB ENQUIRY NO.</t>
+          <t>COLLECTION MODE</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3099,25 +3099,25 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER3</t>
+          <t>LOANPARAMETER26</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.3.value</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.26.value</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'CB ENQUIRY NO.' → 'LOANPARAMETER3' (frequency=4)</t>
+          <t>Alias match (tier2): 'COLLECTION MODE' → 'LOANPARAMETER143' (frequency=16)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>CB SCORE</t>
+          <t>CB ENQUIRY NO.</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Applicant)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3144,25 +3144,25 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>CBSCORE</t>
+          <t>LOANPARAMETER27</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.creditBureauScore</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>1</v>
+          <t>loanAccount.loanParameters.27.value</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'CB SCORE' matches 'CBSCORE'</t>
+          <t>Alias match (tier3): 'CB ENQUIRY NO.' → 'LOANPARAMETER3' (frequency=4)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>DPD DAY</t>
+          <t>CB SCORE</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Applicant)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3189,25 +3189,25 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>LOANCOAPP1CUSTPARAM4</t>
+          <t>CBSCORE</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.3.value</t>
+          <t>loanAccount.loanAccountAdditional.creditBureauScore</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DPD DAY' → 'LOANCOAPP1CUSTPARAM4' (frequency=11)</t>
+          <t>Exact match: normalized 'CB SCORE' matches 'CBSCORE'</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>TOTAL DPD AMOUNT</t>
+          <t>DPD DAY</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Applicant)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>LOANCOAPP1CUSTPARAM5</t>
+          <t>LOANCOAPP1CUSTPARAM4</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.4.value</t>
+          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.3.value</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'TOTAL DPD AMOUNT' → 'LOANCOAPP1CUSTPARAM5' (frequency=13)</t>
+          <t>Alias match (tier2): 'DPD DAY' → 'LOANCOAPP1CUSTPARAM4' (frequency=11)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3264,40 +3264,40 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LIVE NUMBER OF LOANS</t>
+          <t>TOTAL DPD AMOUNT</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Applicant)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER2</t>
+          <t>LOANCOAPP1CUSTPARAM5</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.2.value</t>
+          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.4.value</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'LIVE NUMBER OF LOANS' → 'LOANPARAMETER2' (frequency=39)</t>
+          <t>Alias match (tier2): 'TOTAL DPD AMOUNT' → 'LOANCOAPP1CUSTPARAM5' (frequency=13)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3309,17 +3309,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>EMI OBLIGATION</t>
+          <t>LIVE NUMBER OF LOANS</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Applicant)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'EMI OBLIGATION' → 'LOANPARAMETER28' (frequency=16)</t>
+          <t>Alias match (tier1): 'LIVE NUMBER OF LOANS' → 'LOANPARAMETER2' (frequency=39)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3354,12 +3354,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BANK NAME</t>
+          <t>EMI OBLIGATION</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Applicant)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CUSTOMERBANK</t>
+          <t>LOANPARAMETER29</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerBankAccounts.0.customerBankName</t>
+          <t>loanAccount.loanParameters.29.value</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BANK NAME' → 'CUSTOMERBANK' (frequency=23)</t>
+          <t>Alias match (tier2): 'EMI OBLIGATION' → 'LOANPARAMETER28' (frequency=16)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>BRANCH NAME</t>
+          <t>BANK NAME</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Bank Details</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER0</t>
+          <t>CUSTOMERBANK</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.0.value</t>
+          <t>loanAccount.customer.customerBankAccounts.0.customerBankName</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BRANCH NAME' → 'LOANPARAMETER0' (frequency=12)</t>
+          <t>Alias match (tier2): 'BANK NAME' → 'CUSTOMERBANK' (frequency=23)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3444,12 +3444,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT NUMBER</t>
+          <t>BRANCH NAME</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Bank Details</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CUSTOMERBANKACCOUNTNUMBER</t>
+          <t>LOANPARAMETER30</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>customer.customerBankAccounts.0.accountNumber</t>
+          <t>loanAccount.loanParameters.30.value</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'ACCOUNT NUMBER' → 'CUSTOMERBANKACCOUNTNUMBER' (frequency=23)</t>
+          <t>Alias match (tier2): 'BRANCH NAME' → 'LOANPARAMETER0' (frequency=12)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>IFSC CODE</t>
+          <t>ACCOUNT NUMBER</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Bank Details</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3504,25 +3504,25 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>IFSCCODE</t>
+          <t>CUSTOMERBANKACCOUNTNUMBER</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>customer.customerBankAccounts.0.ifscCode</t>
+          <t>customer.customerBankAccounts.0.accountNumber</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'IFSC CODE' matches 'IFSCCODE'</t>
+          <t>Alias match (tier2): 'ACCOUNT NUMBER' → 'CUSTOMERBANKACCOUNTNUMBER' (frequency=23)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>APR%</t>
+          <t>IFSC CODE</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Bank Details</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3549,25 +3549,25 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER37</t>
+          <t>IFSCCODE</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.37.value</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n">
-        <v>0.85</v>
+          <t>customer.customerBankAccounts.0.ifscCode</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'APR%' → 'LOANPARAMETER37' (frequency=3)</t>
+          <t>Exact match: normalized 'IFSC CODE' matches 'IFSCCODE'</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLD INCOME</t>
+          <t>APR%</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>10th June</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3594,25 +3594,25 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLDINCOME</t>
+          <t>LOANPARAMETER31</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.netIncomeOfHousehold</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>1</v>
+          <t>loanAccount.loanParameters.31.value</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'HOUSEHOLD INCOME' matches 'HOUSEHOLDINCOME'</t>
+          <t>Alias match (tier3): 'APR%' → 'LOANPARAMETER37' (frequency=3)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLD EXPENSE</t>
+          <t>HOUSEHOLD INCOME</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>10th June</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3639,25 +3639,25 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER38</t>
+          <t>HOUSEHOLDINCOME</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.38.value</t>
+          <t>loanAccount.loanAccountAdditional.netIncomeOfHousehold</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'HOUSEHOLD EXPENSE' → 'LOANPARAMETER38' (frequency=26)</t>
+          <t>Exact match: normalized 'HOUSEHOLD INCOME' matches 'HOUSEHOLDINCOME'</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>FOIR</t>
+          <t>HOUSEHOLD EXPENSE</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>10th June</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3684,25 +3684,25 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER39</t>
+          <t>LOANPARAMETER32</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.39.value</t>
+          <t>loanAccount.loanParameters.32.value</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'FOIR' → 'LOANPARAMETER39' (frequency=47)</t>
+          <t>Alias match (tier2): 'HOUSEHOLD EXPENSE' → 'LOANPARAMETER38' (frequency=26)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLD_EXPENSE</t>
+          <t>SPOUSE NAME</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3729,25 +3729,25 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER38</t>
+          <t>APPLICANTSPOUSENAME</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.38.value</t>
+          <t>loanAccount.customer.spouseFirstName</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'HOUSEHOLD_EXPENSE' → 'LOANPARAMETER38' (frequency=26)</t>
+          <t>Alias match (tier1): 'SPOUSE NAME' → 'APPLICANTSPOUSENAME' (frequency=43)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLD_INCOME</t>
+          <t>FATHER'S NAME</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3774,25 +3774,25 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLDINCOME</t>
+          <t>LOANPARAMETER33</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.netIncomeOfHousehold</t>
+          <t>loanAccount.loanParameters.33.value</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'HOUSEHOLD_INCOME' matches 'HOUSEHOLDINCOME'</t>
+          <t>Alias match (tier2): 'FATHER'S NAME' → 'LOANPARAMETER175' (frequency=10)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DISTRIC</t>
+          <t>MOTHER'S NAME</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3819,25 +3819,25 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>DISTRICT</t>
+          <t>LOANPARAMETER34</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>customer.district</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>0.9333</v>
+          <t>loanAccount.loanParameters.34.value</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Fuzzy: 'DISTRIC' ~ 'DISTRICT' score=0.93</t>
+          <t>Alias match (tier3): 'MOTHER'S NAME' → 'LOANPARAMETER177' (frequency=7)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DISBURSEMENT UTR</t>
+          <t>SURNAME</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3864,25 +3864,25 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>DISBURSEMENTTYPE</t>
+          <t>LOANPARAMETER35</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.disbursement_type</t>
+          <t>loanAccount.loanParameters.35.value</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>0.8125</v>
+        <v>0.85</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Fuzzy: 'DISBURSEMENT UTR' ~ 'DISBURSEMENTTYPE' score=0.81</t>
+          <t>Alias match (tier3): 'SURNAME' → 'LOANPARAMETER75' (frequency=7)</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT'S NAME (SAME AS KYC)</t>
+          <t>CITY</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3909,25 +3909,25 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERNAME</t>
+          <t>APPLICANTCUSTOMERDISTRICT</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.firstName</t>
+          <t>loanAccount.customer.district</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>The field clearly refers to the applicant's name, which corresponds to APPLICANTCUSTOMERNAME.</t>
+          <t>Alias match (tier1): 'CITY' → 'APPLICANTCUSTOMERDISTRICT' (frequency=46)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>RESIDENTIAL ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3954,25 +3954,25 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCOMMADDRESSDOORNO</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.mailingDoorNo</t>
+          <t>customer.state</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>This field represents the first line of the residential address, semantically matching APPLICANTCOMMADDRESSDOORNO.</t>
+          <t>Exact match: normalized 'STATE' matches 'STATE'</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RESIDENTIAL ADDRESS -2(LANDMARK)</t>
+          <t>CAST</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3999,25 +3999,25 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCOMMADDRESSSTREET</t>
+          <t>LOANPARAMETER36</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.mailingStreet</t>
+          <t>loanAccount.loanParameters.36.value</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>This field represents the second line of the residential address, often a landmark, which best fits APPLICANTCOMMADDRESSSTREET.</t>
+          <t>Alias match (tier2): 'CAST' → 'LOANPARAMETER167' (frequency=10)</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RESIDENTIAL ADDRESS -3(AREA)</t>
+          <t>GENDER</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4044,25 +4044,25 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCOMMADDRESSLOCALITY</t>
+          <t>GENDER</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.mailingLocality</t>
+          <t>customer.gender</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>The field 'AREA' is a strong semantic match for APPLICANTCOMMADDRESSLOCALITY.</t>
+          <t>Exact match: normalized 'GENDER' matches 'GENDER'</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>PIN NO.</t>
+          <t>MARITAL STATUS</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4089,25 +4089,25 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCOMMADDRESSPINCODE</t>
+          <t>MARITALSTATUS</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.mailingPincode</t>
+          <t>customer.maritalStatus</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>The field 'PIN NO.' corresponds to the pincode of the residential address, matching APPLICANTCOMMADDRESSPINCODE.</t>
+          <t>Exact match: normalized 'MARITAL STATUS' matches 'MARITALSTATUS'</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>DATE OF BIRTH /DATE OF INCORPORATION</t>
+          <t>CITIZENSHIP</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4134,25 +4134,25 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTDATEOFBIRTH</t>
+          <t>APPLICANTCOUNTRY</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.dateOfBirth</t>
+          <t>loanAccount.customer.country</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>The field contains 'DATE OF BIRTH' which is a clear semantic match for APPLICANTDATEOFBIRTH.</t>
+          <t>Alias match (tier2): 'CITIZENSHIP' → 'APPLICANTCOUNTRY' (frequency=21)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>OFFICE ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)</t>
+          <t>CONTACT NO.</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4179,25 +4179,25 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTBUSINESSADDRESS1</t>
+          <t>LOANPARAMETER37</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.doorNo</t>
+          <t>loanAccount.loanParameters.37.value</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>This field represents the first line of the office/business address, semantically matching APPLICANTBUSINESSADDRESS1.</t>
+          <t>Alias match (tier2): 'CONTACT NO.' → 'LOANPARAMETER77' (frequency=10)</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>OFFICE ADDRESS -2(LANDMARK)</t>
+          <t>OFFICE NAME</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4224,25 +4224,25 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>ADDRESSREMARKS</t>
+          <t>LOANPARAMETER38</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerAdditional.addressRemarks</t>
+          <t>loanAccount.loanParameters.38.value</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>The landmark for an address is additional information which fits well into ADDRESSREMARKS.</t>
+          <t>Alias match (tier3): 'OFFICE NAME' → 'LOANPARAMETER78' (frequency=7)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>OFFICE ADDRESS -3(AREA)</t>
+          <t>DESIGNATION</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4269,25 +4269,25 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTBUSINESSADDRESS2</t>
+          <t>APPLICANTDESIGNATION</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.locality</t>
+          <t>loanAccount.customer.designation</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>The field 'AREA' for the office address is a strong semantic match for APPLICANTBUSINESSADDRESS2 (locality).</t>
+          <t>Alias match (tier2): 'DESIGNATION' → 'APPLICANTDESIGNATION' (frequency=11)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>OFFICE DISTRIC</t>
+          <t>OFFICE CITY</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4314,25 +4314,25 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERDISTRICT</t>
+          <t>LOANPARAMETER39</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.district</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>0.96</v>
+          <t>loanAccount.loanParameters.39.value</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>The field 'OFFICE DISTRIC' is a clear semantic match for APPLICANTCUSTOMERDISTRICT.</t>
+          <t>Alias match (tier3): 'OFFICE CITY' → 'LOANPARAMETER60' (frequency=6)</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>OFFICE PINCODE NO</t>
+          <t>OFFICE STATE</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4359,25 +4359,25 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERPINCODE</t>
+          <t>LOANPARAMETER40</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.pincode</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>0.97</v>
+          <t>loanAccount.loanParameters.40.value</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic_shortcut</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>The term 'pincode' is a standard semantic shortcut for APPLICANTCUSTOMERPINCODE.</t>
+          <t>Alias match (tier3): 'OFFICE STATE' → 'LOANPARAMETER61' (frequency=6)</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>OFFICE CONTACT NO</t>
+          <t>PAN_NO</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4404,25 +4404,25 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTLANDLINENO</t>
+          <t>APPLICANTCUSTOMERPANNO</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.landLineNo</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>0.9399999999999999</v>
+          <t>loanAccount.customer.panNo</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>'Office contact no' is a strong semantic match for a business landline number, mapping to APPLICANTLANDLINENO.</t>
+          <t>Alias match (tier3): 'PAN_NO' → 'APPLICANTCUSTOMERPANNO' (frequency=4)</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>D_LICENSE_NO</t>
+          <t>VOTER_ID</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4449,25 +4449,25 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DRIVINGLICENSENO</t>
+          <t>VOTERID</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerAdditional.drivingLicenseNo</t>
+          <t>loanAccount.customer.customerAdditional.voterId</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>The field 'D_LICENSE_NO' is a clear abbreviation for Driving License Number, which matches DRIVINGLICENSENO.</t>
+          <t>Exact match: normalized 'VOTER_ID' matches 'VOTERID'</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>UDYOG AADHAR NO.</t>
+          <t>PASSPORT_NO</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4494,25 +4494,25 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERUDYAMNO</t>
+          <t>PASSPORTNO</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.enterpriseRegistrations.1.registrationNumber</t>
+          <t>loanAccount.customer.customerAdditional.passportNo</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>'Udyog Aadhar' is semantically equivalent to Udyam registration number, matching APPLICANTCUSTOMERUDYAMNO.</t>
+          <t>Exact match: normalized 'PASSPORT_NO' matches 'PASSPORTNO'</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>PARTNAR GST AMOUNT</t>
+          <t>AADHARCARD</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4539,25 +4539,25 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>FEE9</t>
+          <t>APPLICANTAADHAARNO</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee9</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="n">
-        <v>0.88</v>
+          <t>loanAccount.customer.aadhaarNo</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>llm_pattern_fee</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>The field 'PARTNAR GST AMOUNT' represents a charge, matching the FEE pattern.</t>
+          <t>Alias match (tier2): 'AADHARCARD' → 'APPLICANTAADHAARNO' (frequency=12)</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>PARTNAR INSURANCE</t>
+          <t>GST NUMBER</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>KYC Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -4584,25 +4584,25 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>FEE10</t>
+          <t>GSTNUMBER</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee10</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="n">
-        <v>0.88</v>
+          <t>customer.enterpriseRegistrations.0.registrationNumber</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>llm_pattern_fee</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>The field 'PARTNAR INSURANCE' likely refers to an insurance premium or charge, matching the FEE pattern.</t>
+          <t>Exact match: normalized 'GST NUMBER' matches 'GSTNUMBER'</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>CREDIT BUREAU NAME/TYPE</t>
+          <t>CB ENQUIRY NO.</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -4629,25 +4629,25 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>NAMEOFBUREAU</t>
+          <t>LOANPARAMETER41</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>customer.cbRemarks</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>0.95</v>
+          <t>loanAccount.loanParameters.41.value</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>The field 'CREDIT BUREAU NAME/TYPE' is a strong semantic match for NAMEOFBUREAU.</t>
+          <t>Alias match (tier3): 'CB ENQUIRY NO.' → 'LOANPARAMETER3' (frequency=4)</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TYPE (Proprietor/FIRM/Ltd/Pvt Ltd Etc..)</t>
+          <t>CB SCORE</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4674,25 +4674,25 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>ENTERPRISEBUSINESSCONSTITUTION</t>
+          <t>CBSCORE</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.enterprise.businessConstitution</t>
+          <t>loanAccount.loanAccountAdditional.creditBureauScore</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>The field describes the business legal structure, which is a perfect semantic match for ENTERPRISEBUSINESSCONSTITUTION.</t>
+          <t>Exact match: normalized 'CB SCORE' matches 'CBSCORE'</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4704,27 +4704,27 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TOTAL OUTSTADING OF LIVE LOANS</t>
+          <t>DPD DAY</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>OUTSTANDINGAMOUNT</t>
+          <t>LOANCOAPP1CUSTPARAM4</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.outstandingAmount</t>
+          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.3.value</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
@@ -4732,22 +4732,1327 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
+          <t>alias_tier2</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Alias match (tier2): 'DPD DAY' → 'LOANCOAPP1CUSTPARAM4' (frequency=11)</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL DPD AMOUNT</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Credit Bureau Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>LOANCOAPP1CUSTPARAM5</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.4.value</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>alias_tier2</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Alias match (tier2): 'TOTAL DPD AMOUNT' → 'LOANCOAPP1CUSTPARAM5' (frequency=13)</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>LIVE NUMBER OF LOANS</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Credit Bureau Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER42</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.42.value</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>alias_tier1</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Alias match (tier1): 'LIVE NUMBER OF LOANS' → 'LOANPARAMETER2' (frequency=39)</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>FOIR</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER43</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.43.value</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>alias_tier1</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Alias match (tier1): 'FOIR' → 'LOANPARAMETER39' (frequency=47)</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>HOUSEHOLD_EXPENSE</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>LOANPARAMETER44</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.loanParameters.44.value</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>alias_tier2</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Alias match (tier2): 'HOUSEHOLD_EXPENSE' → 'LOANPARAMETER38' (frequency=26)</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>HOUSEHOLD_INCOME</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>HOUSEHOLDINCOME</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.loanAccountAdditional.netIncomeOfHousehold</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Exact match: normalized 'HOUSEHOLD_INCOME' matches 'HOUSEHOLDINCOME'</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>DISTRIC</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Customer Details</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>DISTRICT</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>customer.district</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>fuzzy</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy: 'DISTRIC' ~ 'DISTRICT' score=0.93</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>CUSTOMER ROI</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Loan Details</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERID</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.oldCustomerId</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>0.8696</v>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>fuzzy</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy: 'CUSTOMER ROI' ~ 'APPLICANTCUSTOMERID' score=0.87</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>DISBURSEMENT UTR</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Loan Details</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>DISBURSEMENTTYPE</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.disbursement_type</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>fuzzy</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy: 'DISBURSEMENT UTR' ~ 'DISBURSEMENTTYPE' score=0.81</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>DISTRIC</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>DISTRICT</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>customer.district</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>fuzzy</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Fuzzy: 'DISTRIC' ~ 'DISTRICT' score=0.93</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>DATE OF BIRTH /DATE OF INCORPORATION</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>DATEOFINCORPORATION</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>customer.enterprise.registrationDate</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>embedding</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Embedding: 'DATE OF BIRTH /DATE OF INCORPORATION' → 'DATEOFINCORPORATION' sim=0.802</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT'S NAME (SAME AS KYC)</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Customer Details</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERNAME</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.firstName</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
           <t>llm_semantic</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>The field semantically maps to 'Outstanding Amount' which represents the amount currently owed on a loan.</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>The field requests the applicant's name, which semantically maps to APPLICANTCUSTOMERNAME representing the first name.</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL ADDRESS -2(LANDMARK)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>LANDMARK</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>customer.landmark</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>The field name contains 'LANDMARK', which directly maps to the LANDMARK excel key.</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>PIN NO.</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERPINCODE</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.pincode</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic_shortcut</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>The field 'PIN NO.' normalizes to 'pincode', which matches the semantic shortcut for APPLICANTCUSTOMERPINCODE.</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>OFFICE ADDRESS -3(AREA)</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTBUSINESSADDRESS2</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.locality</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>The term 'AREA' semantically matches 'locality', which is the description for APPLICANTBUSINESSADDRESS2.</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>OFFICE PINCODE NO</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTCOMMADDRESSPINCODE</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.mailingPincode</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>This field represents the pincode for an office address, which is a type of communication address, matching APPLICANTCOMMADDRESSPINCODE.</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>CREDIT BUREAU NAME/TYPE</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Credit Bureau Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>NAMEOFBUREAU</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>customer.cbRemarks</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>The field asks for the credit bureau name, which is a strong semantic match for NAMEOFBUREAU.</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>SEGMENT NAME</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Partner Details</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERCATEGORY</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.customerCategory</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>'Segment Name' can be interpreted as the customer's category or segment, which semantically maps to APPLICANTCUSTOMERCATEGORY.</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTBUSINESSADDRESS1</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.doorNo</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>This field for the first line of a residential address maps well to APPLICANTBUSINESSADDRESS1, described as 'Customer door number'.</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL ADDRESS -3(AREA)</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTBUSINESSADDRESS2</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.locality</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>The term 'AREA' strongly corresponds to 'locality', which is the path for APPLICANTBUSINESSADDRESS2.</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>OFFICE ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>ADDRESSOFFPO</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.enterprise.businessAddress1</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>This field represents the first line of an office address, which is a good semantic match for ADDRESSOFFPO (businessAddress1).</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>OFFICE DISTRIC</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTCOMMADDRESSDISTRICT</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.mailingDistrict</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>'OFFICE DISTRIC' (district) maps to the communication address district, as office address is a form of communication address.</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>OFFICE CONTACT NO</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTLANDLINENO</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.landLineNo</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>An office contact number is often a landline, making APPLICANTLANDLINENO a strong semantic match.</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>D_LICENSE_NO</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>KYC Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>DRIVINGLICENSENO</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.customerAdditional.drivingLicenseNo</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>'D_LICENSE_NO' is a clear abbreviation for Driving License Number, which matches DRIVINGLICENSENO.</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>UDYOG AADHAR NO.</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>KYC Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERUDYAMNO</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.enterpriseRegistrations.1.registrationNumber</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>'Udyog Aadhar' is the former name for Udyam registration, making this a direct semantic match to APPLICANTCUSTOMERUDYAMNO.</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>PARTNAR GST AMOUNT</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Loan Details</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>FEE9</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.fee9</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>llm_pattern_fee</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>This field represents a GST amount related to the partner, which can be categorized as a fee or charge.</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>PARTNAR INSURANCE</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Loan Details</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>FEE10</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.fee10</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>llm_pattern_fee</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>This field represents an insurance charge related to the partner, which is a type of fee.</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>PARTNER_PAYMENT</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Loan Details</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>FEE11</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.fee11</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>llm_pattern_fee</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>This field appears to be a payment or charge related to a partner, fitting the FEE category.</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>TYPE (Proprietor/FIRM/Ltd/Pvt Ltd Etc..)</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>ENTERPRISEBUSINESSCONSTITUTION</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.enterprise.businessConstitution</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>The examples provided (Proprietor, FIRM, etc.) are types of business constitution, which is an exact match for ENTERPRISEBUSINESSCONSTITUTION.</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>FOIR%</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM39</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.38.value</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic_shortcut</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>The term 'foir' has a semantic shortcut mapping to a generic loan parameter, correctly identified as LOANAPPLICANTPARAM39.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I94"/>
+  <autoFilter ref="A1:I123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4758,7 +6063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4775,7 +6080,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>indifi</t>
+          <t>INDIFI</t>
         </is>
       </c>
     </row>
@@ -4799,7 +6104,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-27 15:52:16</t>
+          <t>2026-04-06 12:24:31</t>
         </is>
       </c>
     </row>
@@ -4810,7 +6115,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>106</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
@@ -4820,7 +6125,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -4847,7 +6152,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -4857,7 +6162,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -4867,7 +6172,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -4877,195 +6182,191 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>embedding</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>fuzzy</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>llm_pattern_fee</t>
+          <t>llm_customerparameter</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>llm_loanparameter</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>llm_semantic_shortcut</t>
+          <t>llm_pattern_fee</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>llm_semantic_shortcut</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
           <t>llm_unmatched</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Breakdown by Entity:</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>FEE</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FEE</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
           <t>LOAN</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Fields Needing Review:</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B30" s="7" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
+    <row r="31">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Fields:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>BANK_BENEF_NAME</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SEGMENT NAME</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>DEPARMENT</t>
+          <t>LOAN AMOUNT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>DISB. AMOUNT</t>
+          <t>BANK_BENEF_NAME</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>GROSS TENURE</t>
+          <t>OFFICE ADDRESS -2(LANDMARK)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5077,55 +6378,55 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>NET TENURE</t>
+          <t>DISB. AMOUNT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>PARTNER_PAYMENT</t>
+          <t>GROSS TENURE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>NETDISBAMT</t>
+          <t>NET TENURE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>DATE &amp; TIME</t>
+          <t>NETDISBAMT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>No. of WOMAN AS CEO/COO/PRESIDENT/VICE-PRESIDENT/DIRECTOR etc…. In this designation</t>
+          <t>DEPARMENT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5137,7 +6438,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>% OWNED BY WOMAN/WOMEN</t>
+          <t>DATE &amp; TIME</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5149,7 +6450,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>FOIR%</t>
+          <t>No. of WOMAN AS CEO/COO/PRESIDENT/VICE-PRESIDENT/DIRECTOR etc…. In this designation</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5161,59 +6462,83 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
+          <t>% OWNED BY WOMAN/WOMEN</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TOTAL OUTSTADING OF LIVE LOANS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
           <t>CO- APPLICANT'S NAME (SAME AS KYC)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Confidence Distribution:</t>
         </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>0.90-1.00</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.80-0.89</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.70-0.79</t>
+          <t>0.90-1.00</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
+          <t>0.80-0.89</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0.70-0.79</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
           <t>0.00-0.69</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5292,27 +6617,27 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>BANK_BENEF_NAME</t>
+          <t>LOAN AMOUNT</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>APPLICANTNAMEINBANKACCOUNT</t>
+          <t>DISBURSEMENTAMOUNT</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>APPLICANTNAMEINBANKACCOUNT</t>
+          <t>loanAccount.disbursementSchedules.0.disbursementAmount</t>
         </is>
       </c>
       <c r="F2" s="9" t="n">
@@ -5325,7 +6650,7 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Alias match (tier4): 'BANK_BENEF_NAME' → 'APPLICANTNAMEINBANKACCOUNT' (frequency=1)</t>
+          <t>Alias match (tier4): 'LOAN AMOUNT' → 'DISBURSEMENTAMOUNT' (frequency=1)</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
@@ -5337,12 +6662,12 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>SEGMENT NAME</t>
+          <t>BANK_BENEF_NAME</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Bank Details</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -5352,25 +6677,25 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>APPLICANTNAMEINBANKACCOUNT</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>APPLICANTNAMEINBANKACCOUNT</t>
         </is>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>alias_tier4</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>The field 'SEGMENT NAME' is a generic applicant parameter with no specific excel_key match.</t>
+          <t>Alias match (tier4): 'BANK_BENEF_NAME' → 'APPLICANTNAMEINBANKACCOUNT' (frequency=1)</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -5382,12 +6707,12 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>DEPARMENT</t>
+          <t>OFFICE ADDRESS -2(LANDMARK)</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -5397,12 +6722,12 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM1</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM1</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
@@ -5415,7 +6740,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>The field 'DEPARMENT' is a specific applicant detail with no direct excel_key match, so it falls back to a customer parameter.</t>
+          <t>There is no specific field for an office or business landmark in the available keys.</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -5432,7 +6757,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -5442,25 +6767,25 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANPARAMETER45</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.loanParameters.45.value</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanparameter</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>The field 'DISB. AMOUNT' is a loan-level concept but the entity is APPLICANT, so it is mapped to a generic CUSTOMERPARAMETER.</t>
+          <t>This is a standard loan attribute but no specific 'disbursement amount' key exists in the provided list.</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -5477,7 +6802,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -5487,25 +6812,25 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANPARAMETER46</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.loanParameters.46.value</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanparameter</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>The field 'GROSS TENURE' is a loan-level concept but the entity is APPLICANT, so it is mapped to a generic CUSTOMERPARAMETER.</t>
+          <t>This is a standard loan attribute but no specific 'tenure' key exists in the provided list.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -5522,7 +6847,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -5532,25 +6857,25 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANPARAMETER47</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.loanParameters.47.value</t>
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanparameter</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>The field 'NET TENURE' is a loan-level concept but the entity is APPLICANT, so it is mapped to a generic CUSTOMERPARAMETER.</t>
+          <t>This is a standard loan attribute but no specific 'tenure' key exists in the provided list.</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -5562,12 +6887,12 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>PARTNER_PAYMENT</t>
+          <t>NETDISBAMT</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -5577,25 +6902,25 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANPARAMETER48</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.loanParameters.48.value</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanparameter</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>The field 'PARTNER_PAYMENT' is a generic applicant parameter with no specific excel_key match.</t>
+          <t>This is a standard loan attribute for net disbursement amount, but no specific key exists in the provided list.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
@@ -5607,12 +6932,12 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NETDISBAMT</t>
+          <t>DEPARMENT</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -5622,12 +6947,12 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM2</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM2</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
@@ -5640,7 +6965,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>The field 'NETDISBAMT' is a loan-level concept but the entity is APPLICANT, so it is mapped to a generic CUSTOMERPARAMETER.</t>
+          <t>There is no specific field available for an applicant's department.</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
@@ -5657,7 +6982,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5667,12 +6992,12 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM3</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM3</t>
         </is>
       </c>
       <c r="F10" s="9" t="n">
@@ -5685,7 +7010,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>The field 'DATE &amp; TIME' is too generic to map to a specific excel_key and falls back to a customer parameter.</t>
+          <t>The field 'DATE &amp; TIME' is too generic and, despite its category hint, does not match any specific date field in the available list.</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
@@ -5702,7 +7027,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>10th June</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -5712,12 +7037,12 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM4</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM4</t>
         </is>
       </c>
       <c r="F11" s="9" t="n">
@@ -5730,7 +7055,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>This is a very specific applicant/enterprise detail with no corresponding excel_key, mapping to CUSTOMERPARAMETER.</t>
+          <t>This is a very specific data point about the number of women in leadership for which no dedicated field exists.</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -5747,7 +7072,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>10th June</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5757,12 +7082,12 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM5</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>CUSTOMERPARAM5</t>
         </is>
       </c>
       <c r="F12" s="9" t="n">
@@ -5775,7 +7100,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>This is a specific applicant/enterprise detail with no corresponding excel_key, mapping to CUSTOMERPARAMETER.</t>
+          <t>This is a specific data point about percentage of ownership by women for which no dedicated field exists.</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
@@ -5787,40 +7112,40 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>FOIR%</t>
+          <t>TOTAL OUTSTADING OF LIVE LOANS</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Credit Bureau Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>LOANPARAMETER49</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>CUSTOMERPARAMETER</t>
+          <t>loanAccount.loanParameters.49.value</t>
         </is>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_loanparameter</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>The field FOIR is a specific financial metric for the applicant with no direct excel_key match, falling back to CUSTOMERPARAMETER.</t>
+          <t>The field represents a specific credit bureau attribute for a co-applicant with no dedicated excel_key, making it a loan-specific parameter.</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
@@ -5837,7 +7162,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Sheet1</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5857,7 +7182,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>The field refers to a COAPPLICANT, but the entity scope is APPLICANT, making a valid mapping impossible.</t>
+          <t>There are no available excel keys for a co-applicant's name in the provided list.</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">

--- a/app/pipeline_output/INDIFI/mapping_INDIFI_COMBINED.xlsx
+++ b/app/pipeline_output/INDIFI/mapping_INDIFI_COMBINED.xlsx
@@ -12,8 +12,8 @@
     <sheet name="For Review" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Mapping'!$A$1:$I$123</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'For Review'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Mapping'!$A$1:$I$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'For Review'!$A$1:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,7 +47,7 @@
       <color rgb="00FF0000"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -84,12 +84,6 @@
         <bgColor rgb="00FED8B1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-        <bgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -123,18 +117,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -664,7 +655,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -678,16 +669,16 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BRANCH CLASSIFICATION' → 'LOANPARAMETER10' (frequency=13)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is an operational detail of the lender's branch associated with the loan application, not a customer attribute.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -709,7 +700,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -723,16 +714,16 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CUSTOMER_CENTER' → 'LOANPARAMETER50' (frequency=16)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is an operational detail of the lender's processing center associated with the loan application, not a customer attribute.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -754,7 +745,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -768,16 +759,16 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BRANCH CITY' → 'LOANPARAMETER11' (frequency=14)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The city of the lender's branch is an application-level operational detail.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -799,7 +790,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,16 +804,16 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'BRANCH STATE' → 'LOANPARAMETER51' (frequency=14)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The state of the lender's branch is an application-level operational detail.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -889,7 +880,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,16 +894,16 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'FIELD EXECUTIVE NAME' → 'LOANPARAMETER6' (frequency=20)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The name of the sales executive handling the application is an operational field related to the loan process.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -934,7 +925,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -948,16 +939,16 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DEALER NAME' → 'LOANPARAMETER122' (frequency=12)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Refers to the dealer involved in the loan transaction, which is part of the loan's sourcing and context, not a detail of the applicant.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -979,7 +970,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -992,17 +983,17 @@
           <t>loanAccount.loanParameters.7.value</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>0.85</v>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'SUB DEALER NAME' → 'LOANPARAMETER123' (frequency=7)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Refers to the sub-dealer involved in the loan, which is part of the loan's sourcing and context.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1074,25 +1065,25 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER8</t>
+          <t>LOANAPPLICANTPARAM1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.8.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.0.value</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'FATHER'S NAME' → 'LOANPARAMETER175' (frequency=10)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a core personal identification and family detail of the applicant or co-applicant.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1119,25 +1110,25 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER9</t>
+          <t>LOANAPPLICANTPARAM2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.9.value</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.1.value</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'MOTHER'S NAME' → 'LOANPARAMETER177' (frequency=7)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a core personal identification and family detail of the applicant or co-applicant.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1164,25 +1155,25 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER10</t>
+          <t>LOANAPPLICANTPARAM3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.10.value</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.2.value</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'SURNAME' → 'LOANPARAMETER75' (frequency=7)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The last name of the applicant or co-applicant, a fundamental part of their personal identity.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1299,25 +1290,25 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER11</t>
+          <t>LOANAPPLICANTPARAM4</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.11.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.3.value</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CAST' → 'LOANPARAMETER167' (frequency=10)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a demographic attribute of the applicant or co-applicant.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1524,25 +1515,25 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER12</t>
+          <t>LOANAPPLICANTPARAM5</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.12.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.4.value</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CONTACT NO.' → 'LOANPARAMETER77' (frequency=10)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The personal phone number of the applicant or co-applicant, which is a core contact detail.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1569,25 +1560,25 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER13</t>
+          <t>LOANAPPLICANTPARAM6</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.13.value</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.5.value</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'OFFICE NAME' → 'LOANPARAMETER78' (frequency=7)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The name of the applicant's or co-applicant's employer, which is part of their employment profile.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1659,25 +1650,25 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER14</t>
+          <t>LOANAPPLICANTPARAM7</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.14.value</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.6.value</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'OFFICE CITY' → 'LOANPARAMETER60' (frequency=6)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The city of the applicant's or co-applicant's workplace, which is part of their employment address.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1704,25 +1695,25 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER15</t>
+          <t>LOANAPPLICANTPARAM8</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.15.value</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.7.value</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'OFFICE STATE' → 'LOANPARAMETER61' (frequency=6)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The state of the applicant's or co-applicant's workplace, which is part of their employment address.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1839,25 +1830,25 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER16</t>
+          <t>LOANAPPLICANTPARAM9</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.16.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.8.value</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'NATURE OF BUSINESS' → 'LOANPARAMETER6' (frequency=24)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. Describes the industry or type of business of the applicant, which is a core component of their employment or business profile.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1884,25 +1875,25 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER17</t>
+          <t>LOANAPPLICANTPARAM10</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.17.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.9.value</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'PHYSICAL_DISABILITY' → 'LOANPARAMETER54' (frequency=11)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a personal demographic attribute of the applicant.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1924,30 +1915,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER18</t>
+          <t>LOANPARAMETER8</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.18.value</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>0.92</v>
+          <t>loanAccount.loanParameters.8.value</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.8</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'WEAKER' → 'LOANPARAMETER56' (frequency=11)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a classification or tag applied to the application for policy or scheme purposes, akin to a risk band, and used for loan decisioning.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2014,30 +2005,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER19</t>
+          <t>LOANPARAMETER9</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.19.value</t>
+          <t>loanAccount.loanParameters.9.value</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'GROSS INCOME (Monthly)' → 'LOANPARAMETER106' (frequency=10)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a key financial input for underwriting and calculating loan eligibility metrics like FOIR and repayment capacity.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2329,7 +2320,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2362,54 +2353,54 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>DISB. DATE</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>LOAN AMOUNT</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Loan Details</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>DISBDATE</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanAccountAdditional.lenderApprovalDate</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Exact match: normalized 'DISB. DATE' matches 'DISBDATE'</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>LOAN</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>DISBURSEMENTAMOUNT</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.disbursementSchedules.0.disbursementAmount</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>alias_tier4</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Alias match (tier4): 'LOAN AMOUNT' → 'DISBURSEMENTAMOUNT' (frequency=1)</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>DOWN PAYMENT</t>
+          <t>DISB. DATE</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2419,30 +2410,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER20</t>
+          <t>DISBDATE</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.20.value</t>
+          <t>loanAccount.loanAccountAdditional.lenderApprovalDate</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DOWN PAYMENT' → 'LOANPARAMETER132' (frequency=10)</t>
+          <t>Exact match: normalized 'DISB. DATE' matches 'DISBDATE'</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2454,7 +2445,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>NO. OF INST.</t>
+          <t>DOWN PAYMENT</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2464,30 +2455,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>NUMBEROFINSTALMENTS</t>
+          <t>LOANPARAMETER10</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.tenure</t>
+          <t>loanAccount.loanParameters.10.value</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'NO. OF INST.' → 'NUMBEROFINSTALMENTS' (frequency=10)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a fundamental financial component of the loan's structure and pricing.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2499,7 +2490,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>COLLECTION FREQUENCY</t>
+          <t>NO. OF INST.</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2509,17 +2500,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>REPAYMENTFREQUENCY</t>
+          <t>NUMBEROFINSTALMENTS</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.frequency</t>
+          <t>loanAccount.tenure</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
@@ -2532,7 +2523,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'COLLECTION FREQUENCY' → 'REPAYMENTFREQUENCY' (frequency=10)</t>
+          <t>Alias match (tier2): 'NO. OF INST.' → 'NUMBEROFINSTALMENTS' (frequency=10)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2544,7 +2535,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MAS ROI</t>
+          <t>COLLECTION FREQUENCY</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2554,30 +2545,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>LENDER1INTERESTRATE</t>
+          <t>REPAYMENTFREQUENCY</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.colendingBankInterestRate</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.frequency</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'MAS ROI' → 'LENDER1INTERESTRATE' (frequency=9)</t>
+          <t>Alias match (tier2): 'COLLECTION FREQUENCY' → 'REPAYMENTFREQUENCY' (frequency=10)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2589,7 +2580,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MAS PROCESSING FEES</t>
+          <t>MAS ROI</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2599,30 +2590,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER21</t>
+          <t>LENDER1INTERESTRATE</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.21.value</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>0.92</v>
+          <t>loanAccount.loanAccountAdditional.colendingBankInterestRate</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'MAS PROCESSING FEES' → 'LOANPARAMETER8' (frequency=10)</t>
+          <t>Alias match (tier3): 'MAS ROI' → 'LENDER1INTERESTRATE' (frequency=9)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2634,7 +2625,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MAS GST AMOUNT</t>
+          <t>MAS PROCESSING FEES</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2644,30 +2635,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER22</t>
+          <t>LOANPARAMETER11</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.22.value</t>
+          <t>loanAccount.loanParameters.11.value</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'MAS GST AMOUNT' → 'LOANPARAMETER12' (frequency=10)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a charge associated with the loan itself, not a customer attribute.</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2679,7 +2670,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>PARTNAR PROCESSING FEES</t>
+          <t>MAS GST AMOUNT</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2689,30 +2680,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>FEE6</t>
+          <t>LOANPARAMETER12</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee6</t>
+          <t>loanAccount.loanParameters.12.value</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Fee detection: field contains fee/charge keywords (fee, fees, processing)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a tax amount calculated on loan fees, making it a loan-level financial detail.</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2724,7 +2715,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>PARTNAR OTHER'S CHARGES</t>
+          <t>PARTNAR PROCESSING FEES</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2739,12 +2730,12 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>FEE7</t>
+          <t>FEE1</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee7</t>
+          <t>loanAccount.fee1</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
@@ -2757,7 +2748,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Fee detection: field contains fee/charge keywords (charge, charges)</t>
+          <t>Fee detection: field contains fee/charge keywords (fees, fee, processing)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
@@ -2769,7 +2760,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>STAMP_DUTY</t>
+          <t>PARTNAR OTHER'S CHARGES</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2779,30 +2770,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>FEE5</t>
+          <t>FEE2</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee5</t>
+          <t>loanAccount.fee2</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'STAMP_DUTY' → 'FEE5' (frequency=15)</t>
+          <t>Fee detection: field contains fee/charge keywords (charges, charge)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -2814,7 +2805,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EMI AMOUNT</t>
+          <t>STAMP_DUTY</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2824,17 +2815,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTPROPOSEDEMI</t>
+          <t>FEE3</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.estimatedEmi</t>
+          <t>loanAccount.fee3</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
@@ -2847,7 +2838,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'EMI AMOUNT' → 'APPLICANTPROPOSEDEMI' (frequency=10)</t>
+          <t>Alias match (tier2): 'STAMP_DUTY' → 'FEE5' (frequency=15)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2859,7 +2850,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>1ST EMI DATE</t>
+          <t>EMI AMOUNT</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2869,30 +2860,30 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>FEE8</t>
+          <t>APPLICANTPROPOSEDEMI</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee8</t>
+          <t>loanAccount.estimatedEmi</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Fee detection: field contains fee/charge keywords (emi)</t>
+          <t>Alias match (tier2): 'EMI AMOUNT' → 'APPLICANTPROPOSEDEMI' (frequency=10)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -2904,7 +2895,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LAST EMI DATE</t>
+          <t>1ST EMI DATE</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2914,30 +2905,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>FEE</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>LASTEMIDATE</t>
+          <t>FEE4</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.estimatedDateOfCompletion</t>
+          <t>loanAccount.fee4</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'LAST EMI DATE' matches 'LASTEMIDATE'</t>
+          <t>Fee detection: field contains fee/charge keywords (emi)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2949,7 +2940,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>CUSTOMER_PAYMENT</t>
+          <t>LAST EMI DATE</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2959,30 +2950,30 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER23</t>
+          <t>LASTEMIDATE</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.23.value</t>
+          <t>loanAccount.estimatedDateOfCompletion</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CUSTOMER_PAYMENT' → 'LOANPARAMETER43' (frequency=13)</t>
+          <t>Exact match: normalized 'LAST EMI DATE' matches 'LASTEMIDATE'</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2994,7 +2985,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>CHARGES DEDUCTION</t>
+          <t>CUSTOMER_PAYMENT</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3004,30 +2995,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER24</t>
+          <t>LOANPARAMETER13</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.24.value</t>
+          <t>loanAccount.loanParameters.13.value</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CHARGES DEDUCTION' → 'LOANPARAMETER141' (frequency=10)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Refers to a payment made towards the loan, such as a down payment or fee, and is a loan-level transaction.</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3039,7 +3030,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DISB MODE BY</t>
+          <t>CHARGES DEDUCTION</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3049,30 +3040,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER25</t>
+          <t>LOANPARAMETER14</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.25.value</t>
+          <t>loanAccount.loanParameters.14.value</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DISB MODE BY' → 'LOANPARAMETER142' (frequency=10)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Represents charges deducted from the loan amount during disbursement, a loan-level financial attribute.</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3084,7 +3075,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>COLLECTION MODE</t>
+          <t>DISB MODE BY</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3094,30 +3085,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER26</t>
+          <t>LOANPARAMETER15</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.26.value</t>
+          <t>loanAccount.loanParameters.15.value</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'COLLECTION MODE' → 'LOANPARAMETER143' (frequency=16)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The mode of disbursement is an operational detail of the loan process.</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3129,40 +3120,40 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>CB ENQUIRY NO.</t>
+          <t>COLLECTION MODE</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Credit Bureau Details (Applicant)</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER27</t>
+          <t>LOANPARAMETER16</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.27.value</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.loanParameters.16.value</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'CB ENQUIRY NO.' → 'LOANPARAMETER3' (frequency=4)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The mode of repayment collection is an operational detail of the loan servicing process.</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3174,7 +3165,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CB SCORE</t>
+          <t>CB ENQUIRY NO.</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3184,17 +3175,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>CBSCORE</t>
+          <t>LOANPARAMETER17</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.creditBureauScore</t>
+          <t>loanAccount.loanParameters.17.value</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
@@ -3202,12 +3193,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'CB SCORE' matches 'CBSCORE'</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a unique transactional identifier for the credit bureau check performed for this specific loan application.</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3219,7 +3210,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>DPD DAY</t>
+          <t>CB SCORE</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3234,25 +3225,25 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>LOANCOAPP1CUSTPARAM4</t>
+          <t>CBSCORE</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.3.value</t>
+          <t>loanAccount.loanAccountAdditional.creditBureauScore</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DPD DAY' → 'LOANCOAPP1CUSTPARAM4' (frequency=11)</t>
+          <t>Exact match: normalized 'CB SCORE' matches 'CBSCORE'</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3264,7 +3255,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TOTAL DPD AMOUNT</t>
+          <t>DPD DAY</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3274,17 +3265,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>LOANCOAPP1CUSTPARAM5</t>
+          <t>LOANCOAPP1CUSTPARAM4</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.4.value</t>
+          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.3.value</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
@@ -3297,7 +3288,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'TOTAL DPD AMOUNT' → 'LOANCOAPP1CUSTPARAM5' (frequency=13)</t>
+          <t>Alias match (tier2): 'DPD DAY' → 'LOANCOAPP1CUSTPARAM4' (frequency=11)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3309,7 +3300,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LIVE NUMBER OF LOANS</t>
+          <t>TOTAL DPD AMOUNT</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3319,30 +3310,30 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER28</t>
+          <t>LOANCOAPP1CUSTPARAM5</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.28.value</t>
+          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.4.value</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'LIVE NUMBER OF LOANS' → 'LOANPARAMETER2' (frequency=39)</t>
+          <t>Alias match (tier2): 'TOTAL DPD AMOUNT' → 'LOANCOAPP1CUSTPARAM5' (frequency=13)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3354,7 +3345,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>EMI OBLIGATION</t>
+          <t>LIVE NUMBER OF LOANS</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3369,25 +3360,25 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER29</t>
+          <t>LOANAPPLICANTPARAM11</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.29.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.10.value</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'EMI OBLIGATION' → 'LOANPARAMETER28' (frequency=16)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credit bureau metric that describes the applicant's or co-applicant's existing credit profile and history.</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3399,97 +3390,97 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>BANK NAME</t>
+          <t>EMI OBLIGATION</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
+          <t>Credit Bureau Details (Applicant)</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM12</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.11.value</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>llm_parameter_bucket</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credit bureau metric quantifying the applicant's existing monthly debt obligations, which is part of their personal financial profile.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>BANK_BENEF_NAME</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
           <t>Bank Details</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>CUSTOMERBANK</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.customerBankAccounts.0.customerBankName</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier2</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier2): 'BANK NAME' → 'CUSTOMERBANK' (frequency=23)</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>BRANCH NAME</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Bank Details</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER30</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.30.value</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>alias_tier2</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Alias match (tier2): 'BRANCH NAME' → 'LOANPARAMETER0' (frequency=12)</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANTNAMEINBANKACCOUNT</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANTNAMEINBANKACCOUNT</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>alias_tier4</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Alias match (tier4): 'BANK_BENEF_NAME' → 'APPLICANTNAMEINBANKACCOUNT' (frequency=1)</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ACCOUNT NUMBER</t>
+          <t>BANK NAME</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3504,12 +3495,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CUSTOMERBANKACCOUNTNUMBER</t>
+          <t>CUSTOMERBANK</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>customer.customerBankAccounts.0.accountNumber</t>
+          <t>loanAccount.customer.customerBankAccounts.0.customerBankName</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
@@ -3522,7 +3513,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'ACCOUNT NUMBER' → 'CUSTOMERBANKACCOUNTNUMBER' (frequency=23)</t>
+          <t>Alias match (tier2): 'BANK NAME' → 'CUSTOMERBANK' (frequency=23)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3534,7 +3525,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>IFSC CODE</t>
+          <t>BRANCH NAME</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3544,17 +3535,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>IFSCCODE</t>
+          <t>LOANPARAMETER18</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>customer.customerBankAccounts.0.ifscCode</t>
+          <t>loanAccount.loanParameters.18.value</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
@@ -3562,12 +3553,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'IFSC CODE' matches 'IFSCCODE'</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Refers to the lender's branch, which is an operational detail related to the loan application's processing.</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3579,12 +3570,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>APR%</t>
+          <t>ACCOUNT NUMBER</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>10th June</t>
+          <t>Bank Details</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3594,25 +3585,25 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER31</t>
+          <t>CUSTOMERBANKACCOUNTNUMBER</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.31.value</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="n">
-        <v>0.85</v>
+          <t>customer.customerBankAccounts.0.accountNumber</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'APR%' → 'LOANPARAMETER37' (frequency=3)</t>
+          <t>Alias match (tier2): 'ACCOUNT NUMBER' → 'CUSTOMERBANKACCOUNTNUMBER' (frequency=23)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3624,12 +3615,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLD INCOME</t>
+          <t>IFSC CODE</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10th June</t>
+          <t>Bank Details</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3639,12 +3630,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLDINCOME</t>
+          <t>IFSCCODE</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.netIncomeOfHousehold</t>
+          <t>customer.customerBankAccounts.0.ifscCode</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
@@ -3657,7 +3648,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'HOUSEHOLD INCOME' matches 'HOUSEHOLDINCOME'</t>
+          <t>Exact match: normalized 'IFSC CODE' matches 'IFSCCODE'</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3669,7 +3660,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLD EXPENSE</t>
+          <t>APR%</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3679,30 +3670,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER32</t>
+          <t>LOANPARAMETER19</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.32.value</t>
+          <t>loanAccount.loanParameters.19.value</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'HOUSEHOLD EXPENSE' → 'LOANPARAMETER38' (frequency=26)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. The Annual Percentage Rate is a core pricing parameter of the loan.</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3714,12 +3705,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SPOUSE NAME</t>
+          <t>HOUSEHOLD INCOME</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Co-applicant Details</t>
+          <t>10th June</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3729,25 +3720,25 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTSPOUSENAME</t>
+          <t>HOUSEHOLDINCOME</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.spouseFirstName</t>
+          <t>loanAccount.loanAccountAdditional.netIncomeOfHousehold</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'SPOUSE NAME' → 'APPLICANTSPOUSENAME' (frequency=43)</t>
+          <t>Exact match: normalized 'HOUSEHOLD INCOME' matches 'HOUSEHOLDINCOME'</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3759,12 +3750,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>FATHER'S NAME</t>
+          <t>HOUSEHOLD EXPENSE</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Co-applicant Details</t>
+          <t>10th June</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3774,12 +3765,12 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER33</t>
+          <t>LOANAPPLICANTPARAM13</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.33.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.12.value</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
@@ -3792,7 +3783,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'FATHER'S NAME' → 'LOANPARAMETER175' (frequency=10)</t>
+          <t>Alias match (tier2): 'HOUSEHOLD EXPENSE' → 'LOANPARAMETER38' (frequency=26)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3804,7 +3795,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MOTHER'S NAME</t>
+          <t>SPOUSE NAME</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3814,30 +3805,30 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER34</t>
+          <t>COAPPLICANT1SPOUSENAME</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.34.value</t>
+          <t>loanAccount.coapplicant.0.spouseFirstName</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'MOTHER'S NAME' → 'LOANPARAMETER177' (frequency=7)</t>
+          <t>Alias match (tier1): 'SPOUSE NAME' → 'APPLICANTSPOUSENAME' (frequency=43); entity substitution applied: COAPPLICANT1SPOUSENAME</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3849,7 +3840,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SURNAME</t>
+          <t>FATHER'S NAME</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3864,25 +3855,25 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER35</t>
+          <t>LOANAPPLICANTPARAM14</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.35.value</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.13.value</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'SURNAME' → 'LOANPARAMETER75' (frequency=7)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a core personal identification and family detail of the applicant or co-applicant.</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3894,7 +3885,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>CITY</t>
+          <t>MOTHER'S NAME</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3909,25 +3900,25 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERDISTRICT</t>
+          <t>LOANAPPLICANTPARAM15</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.district</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.14.value</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'CITY' → 'APPLICANTCUSTOMERDISTRICT' (frequency=46)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a core personal identification and family detail of the applicant or co-applicant.</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3939,7 +3930,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>SURNAME</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3954,12 +3945,12 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>LOANAPPLICANTPARAM16</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>customer.state</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.15.value</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
@@ -3967,12 +3958,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'STATE' matches 'STATE'</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The last name of the applicant or co-applicant, a fundamental part of their personal identity.</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3984,7 +3975,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>CAST</t>
+          <t>CITY</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3999,25 +3990,25 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER36</t>
+          <t>APPLICANTCUSTOMERDISTRICT</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.36.value</t>
+          <t>loanAccount.customer.district</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>alias_tier1</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CAST' → 'LOANPARAMETER167' (frequency=10)</t>
+          <t>Alias match (tier1): 'CITY' → 'APPLICANTCUSTOMERDISTRICT' (frequency=46)</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -4029,7 +4020,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GENDER</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4044,12 +4035,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>GENDER</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>customer.gender</t>
+          <t>customer.state</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
@@ -4062,7 +4053,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'GENDER' matches 'GENDER'</t>
+          <t>Exact match: normalized 'STATE' matches 'STATE'</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4074,7 +4065,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>MARITAL STATUS</t>
+          <t>CAST</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4089,12 +4080,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>MARITALSTATUS</t>
+          <t>LOANAPPLICANTPARAM17</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>customer.maritalStatus</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.16.value</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
@@ -4102,12 +4093,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'MARITAL STATUS' matches 'MARITALSTATUS'</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a demographic attribute of the applicant or co-applicant.</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4119,7 +4110,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>CITIZENSHIP</t>
+          <t>GENDER</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4134,25 +4125,25 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCOUNTRY</t>
+          <t>GENDER</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.country</t>
+          <t>customer.gender</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CITIZENSHIP' → 'APPLICANTCOUNTRY' (frequency=21)</t>
+          <t>Exact match: normalized 'GENDER' matches 'GENDER'</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4164,7 +4155,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>CONTACT NO.</t>
+          <t>MARITAL STATUS</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4179,25 +4170,25 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER37</t>
+          <t>MARITALSTATUS</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.37.value</t>
+          <t>customer.maritalStatus</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'CONTACT NO.' → 'LOANPARAMETER77' (frequency=10)</t>
+          <t>Exact match: normalized 'MARITAL STATUS' matches 'MARITALSTATUS'</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4209,7 +4200,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>OFFICE NAME</t>
+          <t>CITIZENSHIP</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4219,30 +4210,30 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER38</t>
+          <t>COAPPLICANT1COUNTRY</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.38.value</t>
+          <t>loanAccount.coapplicant.0.country</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.85</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'OFFICE NAME' → 'LOANPARAMETER78' (frequency=7)</t>
+          <t>Alias match (tier2): 'CITIZENSHIP' → 'APPLICANTCOUNTRY' (frequency=21); entity substitution applied: COAPPLICANT1COUNTRY</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4254,7 +4245,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>DESIGNATION</t>
+          <t>CONTACT NO.</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4269,25 +4260,25 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTDESIGNATION</t>
+          <t>LOANAPPLICANTPARAM18</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.designation</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.17.value</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DESIGNATION' → 'APPLICANTDESIGNATION' (frequency=11)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The personal phone number of the applicant or co-applicant, which is a core contact detail.</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4299,7 +4290,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>OFFICE CITY</t>
+          <t>OFFICE NAME</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4314,25 +4305,25 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER39</t>
+          <t>LOANAPPLICANTPARAM19</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.39.value</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.18.value</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'OFFICE CITY' → 'LOANPARAMETER60' (frequency=6)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The name of the applicant's or co-applicant's employer, which is part of their employment profile.</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4344,7 +4335,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>OFFICE STATE</t>
+          <t>DESIGNATION</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4359,25 +4350,25 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER40</t>
+          <t>APPLICANTDESIGNATION</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.40.value</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.designation</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'OFFICE STATE' → 'LOANPARAMETER61' (frequency=6)</t>
+          <t>Alias match (tier2): 'DESIGNATION' → 'APPLICANTDESIGNATION' (frequency=11)</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4389,12 +4380,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>PAN_NO</t>
+          <t>OFFICE CITY</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>KYC Details (Co-Applicant)</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4404,25 +4395,25 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERPANNO</t>
+          <t>LOANAPPLICANTPARAM20</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.panNo</t>
-        </is>
-      </c>
-      <c r="F87" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.19.value</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'PAN_NO' → 'APPLICANTCUSTOMERPANNO' (frequency=4)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The city of the applicant's or co-applicant's workplace, which is part of their employment address.</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4434,12 +4425,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>VOTER_ID</t>
+          <t>OFFICE STATE</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>KYC Details (Co-Applicant)</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4449,12 +4440,12 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>VOTERID</t>
+          <t>LOANAPPLICANTPARAM21</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerAdditional.voterId</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.20.value</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
@@ -4462,12 +4453,12 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'VOTER_ID' matches 'VOTERID'</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. The state of the applicant's or co-applicant's workplace, which is part of their employment address.</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4479,7 +4470,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>PASSPORT_NO</t>
+          <t>PAN_NO</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4494,25 +4485,25 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>PASSPORTNO</t>
+          <t>APPLICANTCUSTOMERPANNO</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerAdditional.passportNo</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>1</v>
+          <t>loanAccount.customer.panNo</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>0.85</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>alias_tier3</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'PASSPORT_NO' matches 'PASSPORTNO'</t>
+          <t>Alias match (tier3): 'PAN_NO' → 'APPLICANTCUSTOMERPANNO' (frequency=4)</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4524,7 +4515,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AADHARCARD</t>
+          <t>VOTER_ID</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4539,25 +4530,25 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTAADHAARNO</t>
+          <t>VOTERID</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.aadhaarNo</t>
+          <t>loanAccount.customer.customerAdditional.voterId</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'AADHARCARD' → 'APPLICANTAADHAARNO' (frequency=12)</t>
+          <t>Exact match: normalized 'VOTER_ID' matches 'VOTERID'</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4569,7 +4560,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GST NUMBER</t>
+          <t>PASSPORT_NO</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4584,12 +4575,12 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>GSTNUMBER</t>
+          <t>PASSPORTNO</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>customer.enterpriseRegistrations.0.registrationNumber</t>
+          <t>loanAccount.customer.customerAdditional.passportNo</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
@@ -4602,7 +4593,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'GST NUMBER' matches 'GSTNUMBER'</t>
+          <t>Exact match: normalized 'PASSPORT_NO' matches 'PASSPORTNO'</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4614,12 +4605,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>CB ENQUIRY NO.</t>
+          <t>AADHARCARD</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Credit Bureau Details (Co-Applicant)</t>
+          <t>KYC Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -4629,25 +4620,25 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER41</t>
+          <t>APPLICANTAADHAARNO</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.41.value</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="n">
-        <v>0.85</v>
+          <t>loanAccount.customer.aadhaarNo</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.92</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>alias_tier3</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier3): 'CB ENQUIRY NO.' → 'LOANPARAMETER3' (frequency=4)</t>
+          <t>Alias match (tier2): 'AADHARCARD' → 'APPLICANTAADHAARNO' (frequency=12)</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4659,12 +4650,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>CB SCORE</t>
+          <t>GST NUMBER</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Credit Bureau Details (Co-Applicant)</t>
+          <t>KYC Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4674,12 +4665,12 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>CBSCORE</t>
+          <t>GSTNUMBER</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.creditBureauScore</t>
+          <t>customer.enterpriseRegistrations.0.registrationNumber</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
@@ -4692,7 +4683,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'CB SCORE' matches 'CBSCORE'</t>
+          <t>Exact match: normalized 'GST NUMBER' matches 'GSTNUMBER'</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4704,7 +4695,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>DPD DAY</t>
+          <t>CB ENQUIRY NO.</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4714,30 +4705,30 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>LOANCOAPP1CUSTPARAM4</t>
+          <t>LOANPARAMETER20</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.3.value</t>
+          <t>loanAccount.loanParameters.20.value</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'DPD DAY' → 'LOANCOAPP1CUSTPARAM4' (frequency=11)</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This is a unique transactional identifier for the credit bureau check performed for this specific loan application.</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4749,7 +4740,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>TOTAL DPD AMOUNT</t>
+          <t>CB SCORE</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4759,30 +4750,30 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>LOANCOAPP1CUSTPARAM5</t>
+          <t>CBSCORE</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.4.value</t>
+          <t>loanAccount.loanAccountAdditional.creditBureauScore</t>
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'TOTAL DPD AMOUNT' → 'LOANCOAPP1CUSTPARAM5' (frequency=13)</t>
+          <t>Exact match: normalized 'CB SCORE' matches 'CBSCORE'</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -4794,7 +4785,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>LIVE NUMBER OF LOANS</t>
+          <t>DPD DAY</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4804,30 +4795,30 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>LOAN</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER42</t>
+          <t>LOANCOAPP1CUSTPARAM4</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.42.value</t>
+          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.3.value</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'LIVE NUMBER OF LOANS' → 'LOANPARAMETER2' (frequency=39)</t>
+          <t>Alias match (tier2): 'DPD DAY' → 'LOANCOAPP1CUSTPARAM4' (frequency=11)</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -4839,40 +4830,40 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>FOIR</t>
+          <t>TOTAL DPD AMOUNT</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>10th June</t>
+          <t>Credit Bureau Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER43</t>
+          <t>LOANCOAPP1CUSTPARAM5</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.43.value</t>
+          <t>loanAccount.coapplicant.0.loanCustomerRelations.loanCustomerParameters.4.value</t>
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>alias_tier1</t>
+          <t>alias_tier2</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier1): 'FOIR' → 'LOANPARAMETER39' (frequency=47)</t>
+          <t>Alias match (tier2): 'TOTAL DPD AMOUNT' → 'LOANCOAPP1CUSTPARAM5' (frequency=13)</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4884,12 +4875,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLD_EXPENSE</t>
+          <t>LIVE NUMBER OF LOANS</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>10th June</t>
+          <t>Credit Bureau Details (Co-Applicant)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -4899,25 +4890,25 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>LOANPARAMETER44</t>
+          <t>LOANAPPLICANTPARAM22</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanParameters.44.value</t>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.21.value</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>alias_tier2</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Alias match (tier2): 'HOUSEHOLD_EXPENSE' → 'LOANPARAMETER38' (frequency=26)</t>
+          <t>Parameter bucket classifier chose LOANAPPLICANTPARAM. This is a credit bureau metric that describes the applicant's or co-applicant's existing credit profile and history.</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -4929,7 +4920,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLD_INCOME</t>
+          <t>FOIR</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4939,17 +4930,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>HOUSEHOLDINCOME</t>
+          <t>LOANPARAMETER21</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.loanAccountAdditional.netIncomeOfHousehold</t>
+          <t>loanAccount.loanParameters.21.value</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
@@ -4957,12 +4948,12 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Exact match: normalized 'HOUSEHOLD_INCOME' matches 'HOUSEHOLDINCOME'</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. Fixed Obligations to Income Ratio is a derived underwriting metric calculated at the application level to determine loan eligibility.</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -4974,40 +4965,40 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>DISTRIC</t>
+          <t>HOUSEHOLD_EXPENSE</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Customer Details</t>
+          <t>10th June</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>DISTRICT</t>
+          <t>LOANPARAMETER22</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>customer.district</t>
+          <t>loanAccount.loanParameters.22.value</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.9333</v>
+        <v>0.9</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Fuzzy: 'DISTRIC' ~ 'DISTRICT' score=0.93</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. A key financial input declared by the applicant and used in underwriting to calculate disposable income and repayment capacity.</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -5019,12 +5010,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>CUSTOMER ROI</t>
+          <t>HOUSEHOLD_INCOME</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Loan Details</t>
+          <t>10th June</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5034,25 +5025,25 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERID</t>
+          <t>HOUSEHOLDINCOME</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.oldCustomerId</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="n">
-        <v>0.8696</v>
+          <t>loanAccount.loanAccountAdditional.netIncomeOfHousehold</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Fuzzy: 'CUSTOMER ROI' ~ 'APPLICANTCUSTOMERID' score=0.87</t>
+          <t>Exact match: normalized 'HOUSEHOLD_INCOME' matches 'HOUSEHOLDINCOME'</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5064,12 +5055,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>DISBURSEMENT UTR</t>
+          <t>DISTRIC</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Loan Details</t>
+          <t>Customer Details</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5079,16 +5070,16 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>DISBURSEMENTTYPE</t>
+          <t>DISTRICT</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.disbursement_type</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="n">
-        <v>0.8125</v>
+          <t>customer.district</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0.9333</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -5097,7 +5088,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Fuzzy: 'DISBURSEMENT UTR' ~ 'DISBURSEMENTTYPE' score=0.81</t>
+          <t>Fuzzy: 'DISTRIC' ~ 'DISTRICT' score=0.93</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5109,31 +5100,31 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>DISTRIC</t>
+          <t>CUSTOMER ROI</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Co-applicant Details</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>DISTRICT</t>
+          <t>CUSTOMERID</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>customer.district</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>0.9333</v>
+          <t>loanAccount.customFields.customerId</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0.8182</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -5142,7 +5133,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Fuzzy: 'DISTRIC' ~ 'DISTRICT' score=0.93</t>
+          <t>Fuzzy: 'CUSTOMER ROI' ~ 'CUSTOMERID' score=0.82</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5154,40 +5145,40 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>DATE OF BIRTH /DATE OF INCORPORATION</t>
+          <t>DISBURSEMENT UTR</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Co-applicant Details</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>DATEOFINCORPORATION</t>
+          <t>DISBURSEMENTAMOUNT</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>customer.enterprise.registrationDate</t>
+          <t>loanAccount.disbursementSchedules.0.disbursementAmount</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>0.802</v>
+        <v>0.8235</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>embedding</t>
+          <t>fuzzy</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Embedding: 'DATE OF BIRTH /DATE OF INCORPORATION' → 'DATEOFINCORPORATION' sim=0.802</t>
+          <t>Fuzzy: 'DISBURSEMENT UTR' ~ 'DISBURSEMENTAMOUNT' score=0.82</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5199,31 +5190,31 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT'S NAME (SAME AS KYC)</t>
+          <t>PARTNAR INSURANCE</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Customer Details</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERNAME</t>
+          <t>INSURANCEAMT</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.firstName</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>0.95</v>
+          <t>loanAccount.insuranceFee</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>0.88</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -5232,7 +5223,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>The field requests the applicant's name, which semantically maps to APPLICANTCUSTOMERNAME representing the first name.</t>
+          <t>The field 'PARTNAR INSURANCE' semantically relates to the insurance amount on the loan.</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5244,27 +5235,27 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RESIDENTIAL ADDRESS -2(LANDMARK)</t>
+          <t>NET TENURE</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Co-applicant Details</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>LANDMARK</t>
+          <t>tenure</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>customer.landmark</t>
+          <t>loanAccount.tenure</t>
         </is>
       </c>
       <c r="F106" s="3" t="n">
@@ -5277,7 +5268,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>The field name contains 'LANDMARK', which directly maps to the LANDMARK excel key.</t>
+          <t>The field 'NET TENURE' clearly represents the loan tenure.</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -5289,40 +5280,40 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>PIN NO.</t>
+          <t>DISB. AMOUNT</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Co-applicant Details</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERPINCODE</t>
+          <t>DISBURSEMENTAMOUNT</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.pincode</t>
+          <t>loanAccount.disbursementSchedules.0.disbursementAmount</t>
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic_shortcut</t>
+          <t>llm_semantic</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>The field 'PIN NO.' normalizes to 'pincode', which matches the semantic shortcut for APPLICANTCUSTOMERPINCODE.</t>
+          <t>The field 'DISB. AMOUNT' is a direct abbreviation for Disbursement Amount.</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5334,27 +5325,27 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>OFFICE ADDRESS -3(AREA)</t>
+          <t>GROSS TENURE</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Co-applicant Details</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTBUSINESSADDRESS2</t>
+          <t>tenure</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.locality</t>
+          <t>loanAccount.tenure</t>
         </is>
       </c>
       <c r="F108" s="3" t="n">
@@ -5367,7 +5358,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>The term 'AREA' semantically matches 'locality', which is the description for APPLICANTBUSINESSADDRESS2.</t>
+          <t>The field 'GROSS TENURE' clearly represents the loan tenure.</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5379,40 +5370,40 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>OFFICE PINCODE NO</t>
+          <t>PARTNER_PAYMENT</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Co-applicant Details</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCOMMADDRESSPINCODE</t>
+          <t>LOANPARAMETER23</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.mailingPincode</t>
+          <t>loanAccount.loanParameters.23.value</t>
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>llm_semantic</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>This field represents the pincode for an office address, which is a type of communication address, matching APPLICANTCOMMADDRESSPINCODE.</t>
+          <t>Parameter bucket classifier chose LOANPARAMETER. This field represents a payment related to the loan, likely a fee or a component of the loan disbursement structure.</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5424,31 +5415,31 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>CREDIT BUREAU NAME/TYPE</t>
+          <t>NETDISBAMT</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Credit Bureau Details (Co-Applicant)</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>NAMEOFBUREAU</t>
+          <t>NETDISBURSEMENTAMOUNT</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>customer.cbRemarks</t>
+          <t>loanAccount.expectedDisbursementAmount</t>
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -5457,7 +5448,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>The field asks for the credit bureau name, which is a strong semantic match for NAMEOFBUREAU.</t>
+          <t>The field 'NETDISBAMT' is a direct abbreviation for Net Disbursement Amount.</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -5469,31 +5460,31 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>SEGMENT NAME</t>
+          <t>PARTNAR GST AMOUNT</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Partner Details</t>
+          <t>Loan Details</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERCATEGORY</t>
+          <t>GSTFEE</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerCategory</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="n">
-        <v>0.88</v>
+          <t>loanAccount.loanAccountAdditional.gstFee</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0.93</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -5502,7 +5493,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>'Segment Name' can be interpreted as the customer's category or segment, which semantically maps to APPLICANTCUSTOMERCATEGORY.</t>
+          <t>The field 'PARTNAR GST AMOUNT' represents a GST fee associated with the loan.</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -5514,7 +5505,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>RESIDENTIAL ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)</t>
+          <t>DISTRIC</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5524,17 +5515,17 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTBUSINESSADDRESS1</t>
+          <t>COAPPLICANT1COMMCITY</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.doorNo</t>
+          <t>loanAccount.coapplicant.0.mailingDistrict</t>
         </is>
       </c>
       <c r="F112" s="3" t="n">
@@ -5547,7 +5538,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>This field for the first line of a residential address maps well to APPLICANTBUSINESSADDRESS1, described as 'Customer door number'.</t>
+          <t>The field 'DISTRIC' is a misspelling of 'district' and the context of other fields suggests it refers to the residential (mailing) district.</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -5557,54 +5548,54 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>RESIDENTIAL ADDRESS -3(AREA)</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL ADDRESS -2(LANDMARK)</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>Co-applicant Details</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
         <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANTBUSINESSADDRESS2</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.locality</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>llm_semantic</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>The term 'AREA' strongly corresponds to 'locality', which is the path for APPLICANTBUSINESSADDRESS2.</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM23</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.22.value</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>A specific field for co-applicant residential address landmark does not exist, so a generic parameter is used.</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>OFFICE ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)</t>
+          <t>DATE OF BIRTH /DATE OF INCORPORATION</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5614,21 +5605,21 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>ADDRESSOFFPO</t>
+          <t>COAPPLICANT1DATEOFBIRTH</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.enterprise.businessAddress1</t>
+          <t>loanAccount.coapplicant.0.dateOfBirth</t>
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -5637,7 +5628,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>This field represents the first line of an office address, which is a good semantic match for ADDRESSOFFPO (businessAddress1).</t>
+          <t>The field 'DATE OF BIRTH /DATE OF INCORPORATION' contains 'DATE OF BIRTH' and the entity scope is COAPPLICANT, indicating a person's birth date.</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5649,7 +5640,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>OFFICE DISTRIC</t>
+          <t>OFFICE ADDRESS -2(LANDMARK)</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5659,17 +5650,17 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCOMMADDRESSDISTRICT</t>
+          <t>COAPPLICANT1COMMLANDMARK</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.mailingDistrict</t>
+          <t>loanAccount.coapplicant.0.landmark</t>
         </is>
       </c>
       <c r="F115" s="3" t="n">
@@ -5682,7 +5673,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>'OFFICE DISTRIC' (district) maps to the communication address district, as office address is a form of communication address.</t>
+          <t>The field 'OFFICE ADDRESS -2(LANDMARK)' corresponds to the co-applicant's business address landmark.</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -5694,7 +5685,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>OFFICE CONTACT NO</t>
+          <t>OFFICE PINCODE NO</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5704,17 +5695,17 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTLANDLINENO</t>
+          <t>COAPPLICANT1PINCODE</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.landLineNo</t>
+          <t>loanAccount.coapplicant.0.pincode</t>
         </is>
       </c>
       <c r="F116" s="3" t="n">
@@ -5727,7 +5718,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>An office contact number is often a landline, making APPLICANTLANDLINENO a strong semantic match.</t>
+          <t>The field 'OFFICE PINCODE NO' corresponds to the co-applicant's business address pincode.</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -5739,27 +5730,27 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>D_LICENSE_NO</t>
+          <t>RESIDENTIAL ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>KYC Details (Co-Applicant)</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>DRIVINGLICENSENO</t>
+          <t>COAPPLICANT1COMMADDRESS1</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.customerAdditional.drivingLicenseNo</t>
+          <t>loanAccount.coapplicant.0.mailingDoorNo</t>
         </is>
       </c>
       <c r="F117" s="3" t="n">
@@ -5772,7 +5763,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>'D_LICENSE_NO' is a clear abbreviation for Driving License Number, which matches DRIVINGLICENSENO.</t>
+          <t>The field 'RESIDENTIAL ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)' clearly represents the first line of the co-applicant's residential (mailing) address.</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -5784,31 +5775,31 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>UDYOG AADHAR NO.</t>
+          <t>RESIDENTIAL ADDRESS -3(AREA)</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>KYC Details (Co-Applicant)</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>APPLICANTCUSTOMERUDYAMNO</t>
+          <t>COAPPLICANTMAILINGADDRESS2</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.enterpriseRegistrations.1.registrationNumber</t>
+          <t>loanAccount.coapplicant.0.mailingLocality</t>
         </is>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -5817,7 +5808,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>'Udyog Aadhar' is the former name for Udyam registration, making this a direct semantic match to APPLICANTCUSTOMERUDYAMNO.</t>
+          <t>The field 'RESIDENTIAL ADDRESS -3(AREA)' corresponds to the area or locality part of the co-applicant's residential (mailing) address.</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -5829,130 +5820,130 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>PARTNAR GST AMOUNT</t>
+          <t>PIN NO.</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Loan Details</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
+          <t>COAPPLICANT1</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1COMMPIN</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.coapplicant.0.mailingPincode</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>The field 'PIN NO.' refers to a pincode, and the context of surrounding fields suggests it is for the residential (mailing) address.</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>DEPARMENT</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>FEE9</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.fee9</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>llm_pattern_fee</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>This field represents a GST amount related to the partner, which can be categorized as a fee or charge.</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>PARTNAR INSURANCE</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Loan Details</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>FEE10</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.fee10</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>llm_pattern_fee</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>This field represents an insurance charge related to the partner, which is a type of fee.</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM24</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.23.value</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the co-applicant's department, so a generic parameter is used.</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PARTNER_PAYMENT</t>
+          <t>OFFICE ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Loan Details</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>FEE11</t>
+          <t>COAPPLICANTBUSINESSADDRESS1</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.fee11</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="n">
-        <v>0.88</v>
+          <t>loanAccount.coapplicant.0.doorNo</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0.96</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>llm_pattern_fee</t>
+          <t>llm_semantic</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>This field appears to be a payment or charge related to a partner, fitting the FEE category.</t>
+          <t>The field 'OFFICE ADDRESS -1 (HOUSE/BLOCK/BUILDING NAME)' clearly represents the first line of the co-applicant's office (business) address.</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -5964,31 +5955,31 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>TYPE (Proprietor/FIRM/Ltd/Pvt Ltd Etc..)</t>
+          <t>OFFICE ADDRESS -3(AREA)</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>10th June</t>
+          <t>Co-applicant Details</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>COAPPLICANT1</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>ENTERPRISEBUSINESSCONSTITUTION</t>
+          <t>COAPPLICANTBUSINESSADDRESS2</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>loanAccount.customer.enterprise.businessConstitution</t>
+          <t>loanAccount.coapplicant.0.locality</t>
         </is>
       </c>
       <c r="F122" s="3" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5988,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>The examples provided (Proprietor, FIRM, etc.) are types of business constitution, which is an exact match for ENTERPRISEBUSINESSCONSTITUTION.</t>
+          <t>The field 'OFFICE ADDRESS -3(AREA)' corresponds to the area or locality part of the co-applicant's office (business) address.</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -6009,50 +6000,635 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>OFFICE DISTRIC</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1DISTRICT</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.coapplicant.0.district</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>The field 'OFFICE DISTRIC' is a misspelling of 'district' and clearly refers to the co-applicant's office (business) district.</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>OFFICE CONTACT NO</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1LANDLINENO</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.coapplicant.0.landLineNo</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>The field 'OFFICE CONTACT NO' is best matched with the co-applicant's landline number, which is often an office number.</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>D_LICENSE_NO</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>KYC Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANTADDITIONALKYC1NUMBER</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.coapplicant.0.additionalKYCs.0.kyc1ProofNumber</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>'D_LICENSE_NO' refers to a Driving License number, which is a type of additional KYC proof number for the co-applicant.</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>UDYOG AADHAR NO.</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>KYC Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANTADDITIONALKYC2NUMBER</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.coapplicant.0.additionalKYCs.1.kyc1ProofNumber</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>'UDYOG AADHAR NO.' refers to an Udyog Aadhar number, which can be mapped as an additional KYC proof number for the co-applicant.</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>CREDIT BUREAU NAME/TYPE</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Credit Bureau Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM25</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the co-applicant's credit bureau name or type, so a generic parameter is used.</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>DATE &amp; TIME</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Credit Bureau Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM26</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.25.value</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the date and time of the co-applicant's credit bureau report, so a generic parameter is used.</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL OUTSTADING OF LIVE LOANS</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Credit Bureau Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1OBLIGATIONALL</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.coapplicant.0.totalExistingObligations</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>'TOTAL OUTSTADING OF LIVE LOANS' is a clear description for the co-applicant's total existing loan obligations.</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>CO- APPLICANT'S NAME (SAME AS KYC)</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1NAME</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.coapplicant.0.firstName</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>The field 'CO- APPLICANT'S NAME' maps to the standard name field for the first co-applicant, which corresponds to the first name.</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT'S NAME (SAME AS KYC)</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Customer Details</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERNAME</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.firstName</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>The field "APPLICANT'S NAME (SAME AS KYC)" directly corresponds to the applicant's name.</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>SEGMENT NAME</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Partner Details</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTCUSTOMERCATEGORY</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.customerCategory</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>'SEGMENT NAME' is a business term often used to mean 'Customer Category'.</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>TYPE (Proprietor/FIRM/Ltd/Pvt Ltd Etc..)</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>APPLICANTBUSINESSTYPE</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.enterprise.enterpriseType</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>llm_semantic</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>The field specifies the business entity type like Proprietor/Firm which directly maps to business type.</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>No. of WOMAN AS CEO/COO/PRESIDENT/VICE-PRESIDENT/DIRECTOR etc…. In this designation</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM27</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.26.value</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the number of women in leadership roles so this maps to a generic applicant parameter.</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>% OWNED BY WOMAN/WOMEN</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANT</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM28</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.27.value</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the percentage of ownership by women so this maps to a generic applicant parameter.</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
           <t>FOIR%</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>10th June</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>LOANAPPLICANTPARAM39</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.38.value</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>llm_semantic_shortcut</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>The term 'foir' has a semantic shortcut mapping to a generic loan parameter, correctly identified as LOANAPPLICANTPARAM39.</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM29</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.28.value</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>FOIR is a standard applicant financial parameter but no specific key is available so it maps to a generic applicant parameter.</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I123"/>
+  <autoFilter ref="A1:I136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6063,7 +6639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6104,7 +6680,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-06 12:24:31</t>
+          <t>2026-04-07 11:11:33</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6690,7 @@
           <t>Total Fields Mapped:</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="7" t="n">
         <v>135</v>
       </c>
     </row>
@@ -6125,7 +6701,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7">
@@ -6135,11 +6711,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Breakdown by Match Type:</t>
         </is>
@@ -6152,7 +6728,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -6162,7 +6738,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -6172,7 +6748,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -6188,27 +6764,27 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>embedding</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>fee</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>fee</t>
+          <t>fuzzy</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -6218,131 +6794,133 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>fuzzy</t>
+          <t>llm_loanapplicantparam</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>llm_customerparameter</t>
+          <t>llm_parameter_bucket</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>llm_loanparameter</t>
+          <t>llm_semantic</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>llm_pattern_fee</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>llm_semantic</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>14</v>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Breakdown by Entity:</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>llm_semantic_shortcut</t>
+          <t>APPLICANT</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>llm_unmatched</t>
+          <t>COAPPLICANT</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>COAPPLICANT1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>21</v>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Breakdown by Entity:</t>
-        </is>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FEE</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>APPLICANT</t>
+          <t>LOAN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>124</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>FEE</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Fields Needing Review:</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Fields Needing Review:</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>13</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fields:</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Fields:</t>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LOAN AMOUNT</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>LOAN AMOUNT</t>
+          <t>BANK_BENEF_NAME</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6354,19 +6932,19 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>BANK_BENEF_NAME</t>
+          <t>RESIDENTIAL ADDRESS -2(LANDMARK)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>OFFICE ADDRESS -2(LANDMARK)</t>
+          <t>DEPARMENT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -6378,55 +6956,55 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>DISB. AMOUNT</t>
+          <t>CREDIT BUREAU NAME/TYPE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>GROSS TENURE</t>
+          <t>DATE &amp; TIME</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>NET TENURE</t>
+          <t>No. of WOMAN AS CEO/COO/PRESIDENT/VICE-PRESIDENT/DIRECTOR etc…. In this designation</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>NETDISBAMT</t>
+          <t>% OWNED BY WOMAN/WOMEN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>DEPARMENT</t>
+          <t>FOIR%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6435,111 +7013,61 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>DATE &amp; TIME</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No. of WOMAN AS CEO/COO/PRESIDENT/VICE-PRESIDENT/DIRECTOR etc…. In this designation</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>% OWNED BY WOMAN/WOMEN</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>TOTAL OUTSTADING OF LIVE LOANS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CO- APPLICANT'S NAME (SAME AS KYC)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Mandatory Fields Missing:</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Confidence Distribution:</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0.90-1.00</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Confidence Distribution:</t>
-        </is>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0.80-0.89</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>0.90-1.00</t>
+          <t>0.70-0.79</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>0.80-0.89</t>
+          <t>0.00-0.69</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>0.70-0.79</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>0.00-0.69</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6553,7 +7081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -6615,584 +7143,412 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>LOAN AMOUNT</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Loan Details</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>LOAN</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>DISBURSEMENTAMOUNT</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>loanAccount.disbursementSchedules.0.disbursementAmount</t>
         </is>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="6" t="n">
         <v>0.75</v>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>alias_tier4</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Alias match (tier4): 'LOAN AMOUNT' → 'DISBURSEMENTAMOUNT' (frequency=1)</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>BANK_BENEF_NAME</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Bank Details</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANTNAMEINBANKACCOUNT</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>APPLICANTNAMEINBANKACCOUNT</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>alias_tier4</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Alias match (tier4): 'BANK_BENEF_NAME' → 'APPLICANTNAMEINBANKACCOUNT' (frequency=1)</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>RESIDENTIAL ADDRESS -2(LANDMARK)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Co-applicant Details</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANTNAMEINBANKACCOUNT</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANTNAMEINBANKACCOUNT</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>alias_tier4</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>Alias match (tier4): 'BANK_BENEF_NAME' → 'APPLICANTNAMEINBANKACCOUNT' (frequency=1)</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM23</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.22.value</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>A specific field for co-applicant residential address landmark does not exist, so a generic parameter is used.</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>OFFICE ADDRESS -2(LANDMARK)</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>DEPARMENT</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Co-applicant Details</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM1</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM1</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="n">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM24</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.23.value</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>0.72</v>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>There is no specific field for an office or business landmark in the available keys.</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the co-applicant's department, so a generic parameter is used.</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>DISB. AMOUNT</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Loan Details</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>CREDIT BUREAU NAME/TYPE</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Credit Bureau Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER45</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.45.value</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>llm_loanparameter</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>This is a standard loan attribute but no specific 'disbursement amount' key exists in the provided list.</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM25</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.24.value</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the co-applicant's credit bureau name or type, so a generic parameter is used.</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>GROSS TENURE</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Loan Details</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>DATE &amp; TIME</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Credit Bureau Details (Co-Applicant)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER46</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.46.value</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>llm_loanparameter</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>This is a standard loan attribute but no specific 'tenure' key exists in the provided list.</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM26</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.25.value</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the date and time of the co-applicant's credit bureau report, so a generic parameter is used.</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>NET TENURE</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Loan Details</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>No. of WOMAN AS CEO/COO/PRESIDENT/VICE-PRESIDENT/DIRECTOR etc…. In this designation</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER47</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.47.value</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>llm_loanparameter</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>This is a standard loan attribute but no specific 'tenure' key exists in the provided list.</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM27</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.26.value</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the number of women in leadership roles so this maps to a generic applicant parameter.</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>NETDISBAMT</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Loan Details</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>% OWNED BY WOMAN/WOMEN</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER48</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.48.value</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>llm_loanparameter</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>This is a standard loan attribute for net disbursement amount, but no specific key exists in the provided list.</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM28</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.27.value</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>No specific field exists for the percentage of ownership by women so this maps to a generic applicant parameter.</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>DEPARMENT</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Co-applicant Details</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>FOIR%</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>10th June</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>APPLICANT</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM2</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM2</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="n">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>LOANAPPLICANTPARAM29</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>loanAccount.customer.loanCustomerRelations.loanCustomerParameters.28.value</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
         <v>0.72</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>There is no specific field available for an applicant's department.</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>llm_loanapplicantparam</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>FOIR is a standard applicant financial parameter but no specific key is available so it maps to a generic applicant parameter.</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>DATE &amp; TIME</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Credit Bureau Details (Co-Applicant)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM3</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM3</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>The field 'DATE &amp; TIME' is too generic and, despite its category hint, does not match any specific date field in the available list.</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>No. of WOMAN AS CEO/COO/PRESIDENT/VICE-PRESIDENT/DIRECTOR etc…. In this designation</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>10th June</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM4</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM4</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>This is a very specific data point about the number of women in leadership for which no dedicated field exists.</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>% OWNED BY WOMAN/WOMEN</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>10th June</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM5</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMERPARAM5</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>llm_customerparameter</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>This is a specific data point about percentage of ownership by women for which no dedicated field exists.</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL OUTSTADING OF LIVE LOANS</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Credit Bureau Details (Co-Applicant)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>LOAN</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>LOANPARAMETER49</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>loanAccount.loanParameters.49.value</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>llm_loanparameter</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>The field represents a specific credit bureau attribute for a co-applicant with no dedicated excel_key, making it a loan-specific parameter.</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>CO- APPLICANT'S NAME (SAME AS KYC)</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Co-applicant Details</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>APPLICANT</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>llm_unmatched</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>There are no available excel keys for a co-applicant's name in the provided list.</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>